--- a/data/sports/npb/gated.xlsx
+++ b/data/sports/npb/gated.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ136" headerRowCount="1">
-  <autoFilter ref="A1:DQ136"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ137" headerRowCount="1">
+  <autoFilter ref="A1:DQ137"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$136)</f>
+        <f>COUNTA('Picks'!$A$2:$A$137)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$136,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$137,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$136,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$137,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$136,"settled",'Picks'!$V$2:$V$136,"win")+COUNTIFS('Picks'!$U$2:$U$136,"settled",'Picks'!$V$2:$V$136,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"win")+COUNTIFS('Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$136,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$137,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$136,"&gt;0",'Picks'!$V$2:$V$136,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$136,"&gt;0",'Picks'!$V$2:$V$136,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$136,"&gt;0",'Picks'!$V$2:$V$136,"win")/(COUNTIFS('Picks'!$BX$2:$BX$136,"&gt;0",'Picks'!$V$2:$V$136,"win")+COUNTIFS('Picks'!$BX$2:$BX$136,"&gt;0",'Picks'!$V$2:$V$136,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"win")/(COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"win")+COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$136)/SUM('Picks'!$BX$2:$BX$136),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$137)/SUM('Picks'!$BX$2:$BX$137),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$136)</f>
+        <f>SUM('Picks'!$BY$2:$BY$137)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$136,"&lt;&gt;",'Picks'!$AB$2:$AB$136),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$137,"&lt;&gt;",'Picks'!$AB$2:$AB$137),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$136,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$136,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$137,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$137,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$136,'Picks'!$AM$2:$AM$136,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$137,'Picks'!$AM$2:$AM$137,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$136,$A14,'Picks'!$U$2:$U$136,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$137,$A14,'Picks'!$U$2:$U$137,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$136,$A14,'Picks'!$U$2:$U$136,"settled",'Picks'!$V$2:$V$136,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$137,$A14,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$136,$A14,'Picks'!$U$2:$U$136,"settled",'Picks'!$V$2:$V$136,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$137,$A14,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$136,'Picks'!$H$2:$H$136,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$137,'Picks'!$H$2:$H$137,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$136,'Picks'!$H$2:$H$136,$A14,'Picks'!$U$2:$U$136,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$137,'Picks'!$H$2:$H$137,$A14,'Picks'!$U$2:$U$137,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$136,$A15,'Picks'!$U$2:$U$136,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$137,$A15,'Picks'!$U$2:$U$137,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$136,$A15,'Picks'!$U$2:$U$136,"settled",'Picks'!$V$2:$V$136,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$137,$A15,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$136,$A15,'Picks'!$U$2:$U$136,"settled",'Picks'!$V$2:$V$136,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$137,$A15,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$136,'Picks'!$H$2:$H$136,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$137,'Picks'!$H$2:$H$137,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$136,'Picks'!$H$2:$H$136,$A15,'Picks'!$U$2:$U$136,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$137,'Picks'!$H$2:$H$137,$A15,'Picks'!$U$2:$U$137,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$136,$A16,'Picks'!$U$2:$U$136,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$137,$A16,'Picks'!$U$2:$U$137,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$136,$A16,'Picks'!$U$2:$U$136,"settled",'Picks'!$V$2:$V$136,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$137,$A16,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$136,$A16,'Picks'!$U$2:$U$136,"settled",'Picks'!$V$2:$V$136,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$137,$A16,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$136,'Picks'!$H$2:$H$136,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$137,'Picks'!$H$2:$H$137,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$136,'Picks'!$H$2:$H$136,$A16,'Picks'!$U$2:$U$136,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$137,'Picks'!$H$2:$H$137,$A16,'Picks'!$U$2:$U$137,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ136"/>
+  <dimension ref="A1:DQ137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19869,18 +19869,28 @@
       </c>
       <c r="U59" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V59" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V59" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W59" s="26" t="n"/>
       <c r="X59" s="26" t="n"/>
       <c r="Y59" s="25" t="n"/>
       <c r="Z59" s="26" t="n"/>
       <c r="AA59" s="28" t="n"/>
       <c r="AB59" s="28" t="n"/>
-      <c r="AC59" s="30" t="n"/>
-      <c r="AD59" s="24" t="n"/>
+      <c r="AC59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:00:21.727605Z</t>
+        </is>
+      </c>
       <c r="AE59" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.4700 (market_slug=aec-npb-tys-cdh-2026-09-06). Tie probability=0.0355.</t>
@@ -20029,7 +20039,11 @@
       <c r="BT59" s="28" t="n"/>
       <c r="BU59" s="25" t="n"/>
       <c r="BV59" s="29" t="n"/>
-      <c r="BW59" s="24" t="n"/>
+      <c r="BW59" s="24" t="inlineStr">
+        <is>
+          <t>NPB game scheduled on 2026-09-06 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX59" s="30" t="n"/>
       <c r="BY59" s="27" t="n"/>
       <c r="BZ59" s="24" t="n"/>
@@ -22092,18 +22106,28 @@
       </c>
       <c r="U66" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V66" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V66" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W66" s="26" t="n"/>
       <c r="X66" s="26" t="n"/>
       <c r="Y66" s="25" t="n"/>
       <c r="Z66" s="26" t="n"/>
       <c r="AA66" s="28" t="n"/>
       <c r="AB66" s="28" t="n"/>
-      <c r="AC66" s="30" t="n"/>
-      <c r="AD66" s="24" t="n"/>
+      <c r="AC66" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:00:24.661915Z</t>
+        </is>
+      </c>
       <c r="AE66" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6700 (market_slug=aec-npb-hta-hci-2026-09-08). Tie probability=0.0201.</t>
@@ -22252,7 +22276,11 @@
       <c r="BT66" s="28" t="n"/>
       <c r="BU66" s="25" t="n"/>
       <c r="BV66" s="29" t="n"/>
-      <c r="BW66" s="24" t="n"/>
+      <c r="BW66" s="24" t="inlineStr">
+        <is>
+          <t>NPB game scheduled on 2026-09-08 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX66" s="30" t="n"/>
       <c r="BY66" s="27" t="n"/>
       <c r="BZ66" s="24" t="n"/>
@@ -25611,18 +25639,28 @@
       </c>
       <c r="U77" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V77" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V77" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W77" s="26" t="n"/>
       <c r="X77" s="26" t="n"/>
       <c r="Y77" s="25" t="n"/>
       <c r="Z77" s="26" t="n"/>
       <c r="AA77" s="28" t="n"/>
       <c r="AB77" s="28" t="n"/>
-      <c r="AC77" s="30" t="n"/>
-      <c r="AD77" s="24" t="n"/>
+      <c r="AC77" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:00:27.544812Z</t>
+        </is>
+      </c>
       <c r="AE77" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-npb-hta-hci-2026-09-10). Tie probability=0.0213.</t>
@@ -25771,7 +25809,11 @@
       <c r="BT77" s="28" t="n"/>
       <c r="BU77" s="25" t="n"/>
       <c r="BV77" s="29" t="n"/>
-      <c r="BW77" s="24" t="n"/>
+      <c r="BW77" s="24" t="inlineStr">
+        <is>
+          <t>NPB game scheduled on 2026-09-10 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX77" s="30" t="n"/>
       <c r="BY77" s="27" t="n"/>
       <c r="BZ77" s="24" t="n"/>
@@ -32322,18 +32364,28 @@
       </c>
       <c r="U98" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V98" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V98" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W98" s="26" t="n"/>
       <c r="X98" s="26" t="n"/>
       <c r="Y98" s="25" t="n"/>
       <c r="Z98" s="26" t="n"/>
       <c r="AA98" s="28" t="n"/>
       <c r="AB98" s="28" t="n"/>
-      <c r="AC98" s="30" t="n"/>
-      <c r="AD98" s="24" t="n"/>
+      <c r="AC98" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:00:30.304593Z</t>
+        </is>
+      </c>
       <c r="AE98" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-npb-clm-ssl-2026-09-20). Tie probability=0.0240.</t>
@@ -32482,7 +32534,11 @@
       <c r="BT98" s="28" t="n"/>
       <c r="BU98" s="25" t="n"/>
       <c r="BV98" s="29" t="n"/>
-      <c r="BW98" s="24" t="n"/>
+      <c r="BW98" s="24" t="inlineStr">
+        <is>
+          <t>NPB game scheduled on 2026-09-20 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX98" s="30" t="n"/>
       <c r="BY98" s="27" t="n"/>
       <c r="BZ98" s="24" t="n"/>
@@ -32623,18 +32679,28 @@
       </c>
       <c r="U99" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V99" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V99" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W99" s="26" t="n"/>
       <c r="X99" s="26" t="n"/>
       <c r="Y99" s="25" t="n"/>
       <c r="Z99" s="26" t="n"/>
       <c r="AA99" s="28" t="n"/>
       <c r="AB99" s="28" t="n"/>
-      <c r="AC99" s="30" t="n"/>
-      <c r="AD99" s="24" t="n"/>
+      <c r="AC99" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:00:33.102064Z</t>
+        </is>
+      </c>
       <c r="AE99" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-npb-trge-fsh-2026-09-21). Tie probability=0.0285.</t>
@@ -32783,7 +32849,11 @@
       <c r="BT99" s="28" t="n"/>
       <c r="BU99" s="25" t="n"/>
       <c r="BV99" s="29" t="n"/>
-      <c r="BW99" s="24" t="n"/>
+      <c r="BW99" s="24" t="inlineStr">
+        <is>
+          <t>NPB game scheduled on 2026-09-21 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX99" s="30" t="n"/>
       <c r="BY99" s="27" t="n"/>
       <c r="BZ99" s="24" t="n"/>
@@ -33869,18 +33939,28 @@
       </c>
       <c r="U103" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V103" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V103" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W103" s="26" t="n"/>
       <c r="X103" s="26" t="n"/>
       <c r="Y103" s="25" t="n"/>
       <c r="Z103" s="26" t="n"/>
       <c r="AA103" s="28" t="n"/>
       <c r="AB103" s="28" t="n"/>
-      <c r="AC103" s="30" t="n"/>
-      <c r="AD103" s="24" t="n"/>
+      <c r="AC103" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD103" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:00:36.091278Z</t>
+        </is>
+      </c>
       <c r="AE103" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-npb-clm-ssl-2026-09-21). Tie probability=0.0349.</t>
@@ -34029,7 +34109,11 @@
       <c r="BT103" s="28" t="n"/>
       <c r="BU103" s="25" t="n"/>
       <c r="BV103" s="29" t="n"/>
-      <c r="BW103" s="24" t="n"/>
+      <c r="BW103" s="24" t="inlineStr">
+        <is>
+          <t>NPB game scheduled on 2026-09-21 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX103" s="30" t="n"/>
       <c r="BY103" s="27" t="n"/>
       <c r="BZ103" s="24" t="n"/>
@@ -40510,18 +40594,38 @@
       </c>
       <c r="U124" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V124" s="24" t="n"/>
-      <c r="W124" s="26" t="n"/>
-      <c r="X124" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V124" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="W124" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X124" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y124" s="25" t="n"/>
-      <c r="Z124" s="26" t="n"/>
-      <c r="AA124" s="28" t="n"/>
-      <c r="AB124" s="28" t="n"/>
-      <c r="AC124" s="30" t="n"/>
-      <c r="AD124" s="24" t="n"/>
+      <c r="Z124" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA124" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB124" s="28" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AC124" s="30" t="n">
+        <v>-0.2059</v>
+      </c>
+      <c r="AD124" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:35.354307Z</t>
+        </is>
+      </c>
       <c r="AE124" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6300 (market_slug=aec-npb-hta-ygo-2026-10-01). Tie probability=0.0238.</t>
@@ -40664,8 +40768,12 @@
       <c r="BN124" s="28" t="n"/>
       <c r="BO124" s="28" t="n"/>
       <c r="BP124" s="25" t="n"/>
-      <c r="BQ124" s="27" t="n"/>
-      <c r="BR124" s="28" t="n"/>
+      <c r="BQ124" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR124" s="28" t="n">
+        <v>0.63</v>
+      </c>
       <c r="BS124" s="28" t="n"/>
       <c r="BT124" s="28" t="n"/>
       <c r="BU124" s="25" t="n"/>
@@ -40811,18 +40919,38 @@
       </c>
       <c r="U125" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V125" s="24" t="n"/>
-      <c r="W125" s="26" t="n"/>
-      <c r="X125" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V125" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W125" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X125" s="26" t="n">
+        <v>5</v>
+      </c>
       <c r="Y125" s="25" t="n"/>
-      <c r="Z125" s="26" t="n"/>
-      <c r="AA125" s="28" t="n"/>
-      <c r="AB125" s="28" t="n"/>
-      <c r="AC125" s="30" t="n"/>
-      <c r="AD125" s="24" t="n"/>
+      <c r="Z125" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA125" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB125" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC125" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD125" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:36.350826Z</t>
+        </is>
+      </c>
       <c r="AE125" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5000 (market_slug=aec-npb-hci-cdh-2026-10-01). Tie probability=0.0238.</t>
@@ -40965,8 +41093,12 @@
       <c r="BN125" s="28" t="n"/>
       <c r="BO125" s="28" t="n"/>
       <c r="BP125" s="25" t="n"/>
-      <c r="BQ125" s="27" t="n"/>
-      <c r="BR125" s="28" t="n"/>
+      <c r="BQ125" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR125" s="28" t="n">
+        <v>0.5</v>
+      </c>
       <c r="BS125" s="28" t="n"/>
       <c r="BT125" s="28" t="n"/>
       <c r="BU125" s="25" t="n"/>
@@ -41112,18 +41244,32 @@
       </c>
       <c r="U126" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V126" s="24" t="n"/>
-      <c r="W126" s="26" t="n"/>
-      <c r="X126" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V126" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W126" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X126" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="Y126" s="25" t="n"/>
       <c r="Z126" s="26" t="n"/>
       <c r="AA126" s="28" t="n"/>
       <c r="AB126" s="28" t="n"/>
-      <c r="AC126" s="30" t="n"/>
-      <c r="AD126" s="24" t="n"/>
+      <c r="AC126" s="30" t="n">
+        <v>0.4926</v>
+      </c>
+      <c r="AD126" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:37.358984Z</t>
+        </is>
+      </c>
       <c r="AE126" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6700 (market_slug=aec-npb-clm-fsh-2026-10-02). Tie probability=0.0238.</t>
@@ -41413,18 +41559,32 @@
       </c>
       <c r="U127" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V127" s="24" t="n"/>
-      <c r="W127" s="26" t="n"/>
-      <c r="X127" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V127" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W127" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X127" s="26" t="n">
+        <v>5</v>
+      </c>
       <c r="Y127" s="25" t="n"/>
       <c r="Z127" s="26" t="n"/>
       <c r="AA127" s="28" t="n"/>
       <c r="AB127" s="28" t="n"/>
-      <c r="AC127" s="30" t="n"/>
-      <c r="AD127" s="24" t="n"/>
+      <c r="AC127" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD127" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:38.326618Z</t>
+        </is>
+      </c>
       <c r="AE127" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5600 (market_slug=aec-npb-tys-ygo-2026-10-02). Tie probability=0.0238.</t>
@@ -41437,7 +41597,7 @@
       </c>
       <c r="AG127" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH127" s="24" t="n"/>
@@ -41714,18 +41874,32 @@
       </c>
       <c r="U128" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V128" s="24" t="n"/>
-      <c r="W128" s="26" t="n"/>
-      <c r="X128" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V128" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W128" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X128" s="26" t="n">
+        <v>6</v>
+      </c>
       <c r="Y128" s="25" t="n"/>
       <c r="Z128" s="26" t="n"/>
       <c r="AA128" s="28" t="n"/>
       <c r="AB128" s="28" t="n"/>
-      <c r="AC128" s="30" t="n"/>
-      <c r="AD128" s="24" t="n"/>
+      <c r="AC128" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD128" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:39.267846Z</t>
+        </is>
+      </c>
       <c r="AE128" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6400 (market_slug=aec-npb-hci-hta-2026-10-03). Tie probability=0.0238.</t>
@@ -41738,7 +41912,7 @@
       </c>
       <c r="AG128" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH128" s="24" t="n"/>
@@ -42015,18 +42189,32 @@
       </c>
       <c r="U129" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V129" s="24" t="n"/>
-      <c r="W129" s="26" t="n"/>
-      <c r="X129" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V129" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W129" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" s="26" t="n">
+        <v>6</v>
+      </c>
       <c r="Y129" s="25" t="n"/>
       <c r="Z129" s="26" t="n"/>
       <c r="AA129" s="28" t="n"/>
       <c r="AB129" s="28" t="n"/>
-      <c r="AC129" s="30" t="n"/>
-      <c r="AD129" s="24" t="n"/>
+      <c r="AC129" s="30" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+      <c r="AD129" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:40.227662Z</t>
+        </is>
+      </c>
       <c r="AE129" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5200 (market_slug=aec-npb-trge-obr-2026-10-03). Tie probability=0.0238.</t>
@@ -42316,18 +42504,32 @@
       </c>
       <c r="U130" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V130" s="24" t="n"/>
-      <c r="W130" s="26" t="n"/>
-      <c r="X130" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V130" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W130" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X130" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y130" s="25" t="n"/>
       <c r="Z130" s="26" t="n"/>
       <c r="AA130" s="28" t="n"/>
       <c r="AB130" s="28" t="n"/>
-      <c r="AC130" s="30" t="n"/>
-      <c r="AD130" s="24" t="n"/>
+      <c r="AC130" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD130" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:41.290300Z</t>
+        </is>
+      </c>
       <c r="AE130" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.4600 (market_slug=aec-npb-tys-cdh-2026-10-03). Tie probability=0.0238.</t>
@@ -42340,7 +42542,7 @@
       </c>
       <c r="AG130" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH130" s="24" t="n"/>
@@ -42617,18 +42819,32 @@
       </c>
       <c r="U131" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V131" s="24" t="n"/>
-      <c r="W131" s="26" t="n"/>
-      <c r="X131" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V131" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W131" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="X131" s="26" t="n">
+        <v>4</v>
+      </c>
       <c r="Y131" s="25" t="n"/>
       <c r="Z131" s="26" t="n"/>
       <c r="AA131" s="28" t="n"/>
       <c r="AB131" s="28" t="n"/>
-      <c r="AC131" s="30" t="n"/>
-      <c r="AD131" s="24" t="n"/>
+      <c r="AC131" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD131" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:42.269185Z</t>
+        </is>
+      </c>
       <c r="AE131" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.4100 (market_slug=aec-npb-tys-hci-2026-10-04). Tie probability=0.0238.</t>
@@ -42641,7 +42857,7 @@
       </c>
       <c r="AG131" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH131" s="24" t="n"/>
@@ -42918,18 +43134,32 @@
       </c>
       <c r="U132" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V132" s="24" t="n"/>
-      <c r="W132" s="26" t="n"/>
-      <c r="X132" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V132" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W132" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X132" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="Y132" s="25" t="n"/>
       <c r="Z132" s="26" t="n"/>
       <c r="AA132" s="28" t="n"/>
       <c r="AB132" s="28" t="n"/>
-      <c r="AC132" s="30" t="n"/>
-      <c r="AD132" s="24" t="n"/>
+      <c r="AC132" s="30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD132" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:43.272037Z</t>
+        </is>
+      </c>
       <c r="AE132" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.4900 (market_slug=aec-npb-clm-trge-2026-10-04). Tie probability=0.0238.</t>
@@ -43219,18 +43449,32 @@
       </c>
       <c r="U133" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V133" s="24" t="n"/>
-      <c r="W133" s="26" t="n"/>
-      <c r="X133" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V133" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W133" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="X133" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y133" s="25" t="n"/>
       <c r="Z133" s="26" t="n"/>
       <c r="AA133" s="28" t="n"/>
       <c r="AB133" s="28" t="n"/>
-      <c r="AC133" s="30" t="n"/>
-      <c r="AD133" s="24" t="n"/>
+      <c r="AC133" s="30" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+      <c r="AD133" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:44.169911Z</t>
+        </is>
+      </c>
       <c r="AE133" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5200 (market_slug=aec-npb-clm-ssl-2026-10-05). Tie probability=0.0238.</t>
@@ -43516,18 +43760,32 @@
       </c>
       <c r="U134" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V134" s="24" t="n"/>
-      <c r="W134" s="26" t="n"/>
-      <c r="X134" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V134" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W134" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X134" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="Y134" s="25" t="n"/>
       <c r="Z134" s="26" t="n"/>
       <c r="AA134" s="28" t="n"/>
       <c r="AB134" s="28" t="n"/>
-      <c r="AC134" s="30" t="n"/>
-      <c r="AD134" s="24" t="n"/>
+      <c r="AC134" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD134" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:45.076259Z</t>
+        </is>
+      </c>
       <c r="AE134" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5900 (market_slug=aec-npb-trge-fsh-2026-10-05). Tie probability=0.0238.</t>
@@ -43540,7 +43798,7 @@
       </c>
       <c r="AG134" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH134" s="24" t="n"/>
@@ -43813,18 +44071,32 @@
       </c>
       <c r="U135" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V135" s="24" t="n"/>
-      <c r="W135" s="26" t="n"/>
-      <c r="X135" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V135" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W135" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X135" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y135" s="25" t="n"/>
       <c r="Z135" s="26" t="n"/>
       <c r="AA135" s="28" t="n"/>
       <c r="AB135" s="28" t="n"/>
-      <c r="AC135" s="30" t="n"/>
-      <c r="AD135" s="24" t="n"/>
+      <c r="AC135" s="30" t="n">
+        <v>0.8197</v>
+      </c>
+      <c r="AD135" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:45.993281Z</t>
+        </is>
+      </c>
       <c r="AE135" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-npb-clm-ssl-2026-10-06). Tie probability=0.0238.</t>
@@ -44110,18 +44382,32 @@
       </c>
       <c r="U136" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V136" s="24" t="n"/>
-      <c r="W136" s="26" t="n"/>
-      <c r="X136" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V136" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W136" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X136" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y136" s="25" t="n"/>
       <c r="Z136" s="26" t="n"/>
       <c r="AA136" s="28" t="n"/>
       <c r="AB136" s="28" t="n"/>
-      <c r="AC136" s="30" t="n"/>
-      <c r="AD136" s="24" t="n"/>
+      <c r="AC136" s="30" t="n">
+        <v>0.5618</v>
+      </c>
+      <c r="AD136" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T23:04:46.986414Z</t>
+        </is>
+      </c>
       <c r="AE136" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6400 (market_slug=aec-npb-hta-hci-2026-10-06). Tie probability=0.0238.</t>
@@ -44326,6 +44612,303 @@
         </is>
       </c>
     </row>
+    <row r="137" ht="36" customHeight="1">
+      <c r="A137" s="24" t="inlineStr">
+        <is>
+          <t>60a44c11dca244c0</t>
+        </is>
+      </c>
+      <c r="B137" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:24:50.453102Z</t>
+        </is>
+      </c>
+      <c r="C137" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D137" s="24" t="inlineStr">
+        <is>
+          <t>142741</t>
+        </is>
+      </c>
+      <c r="E137" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F137" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="G137" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="H137" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I137" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J137" s="25" t="n"/>
+      <c r="K137" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L137" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M137" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N137" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O137" s="28" t="n">
+        <v>0.652882</v>
+      </c>
+      <c r="P137" s="28" t="n"/>
+      <c r="Q137" s="28" t="n">
+        <v>0.043507</v>
+      </c>
+      <c r="R137" s="26" t="n">
+        <v>42</v>
+      </c>
+      <c r="S137" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T137" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U137" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V137" s="24" t="n"/>
+      <c r="W137" s="26" t="n"/>
+      <c r="X137" s="26" t="n"/>
+      <c r="Y137" s="25" t="n"/>
+      <c r="Z137" s="26" t="n"/>
+      <c r="AA137" s="28" t="n"/>
+      <c r="AB137" s="28" t="n"/>
+      <c r="AC137" s="30" t="n"/>
+      <c r="AD137" s="24" t="n"/>
+      <c r="AE137" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-hta-hci-2026-10-07). Tie probability=0.0238.</t>
+        </is>
+      </c>
+      <c r="AF137" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG137" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH137" s="24" t="n"/>
+      <c r="AI137" s="31" t="n"/>
+      <c r="AJ137" s="31" t="n"/>
+      <c r="AK137" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL137" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM137" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN137" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO137" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP137" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AQ137" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AR137" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AS137" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AT137" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AU137" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AV137" s="24" t="n"/>
+      <c r="AW137" s="24" t="n"/>
+      <c r="AX137" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY137" s="24" t="n"/>
+      <c r="AZ137" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA137" s="24" t="inlineStr">
+        <is>
+          <t>52a745e24a739f7876c425755afd5d949b082851299aad8a723cad3af868096f</t>
+        </is>
+      </c>
+      <c r="BB137" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC137" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD137" s="24" t="inlineStr">
+        <is>
+          <t>52a745e24a739f7876c425755afd5d949b082851299aad8a723cad3af868096f</t>
+        </is>
+      </c>
+      <c r="BE137" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF137" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG137" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH137" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:24:50.452100Z</t>
+        </is>
+      </c>
+      <c r="BI137" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ137" s="25" t="n"/>
+      <c r="BK137" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL137" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM137" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN137" s="28" t="n"/>
+      <c r="BO137" s="28" t="n"/>
+      <c r="BP137" s="25" t="n"/>
+      <c r="BQ137" s="27" t="n"/>
+      <c r="BR137" s="28" t="n"/>
+      <c r="BS137" s="28" t="n"/>
+      <c r="BT137" s="28" t="n"/>
+      <c r="BU137" s="25" t="n"/>
+      <c r="BV137" s="29" t="n"/>
+      <c r="BW137" s="24" t="n"/>
+      <c r="BX137" s="30" t="n"/>
+      <c r="BY137" s="27" t="n"/>
+      <c r="BZ137" s="24" t="n"/>
+      <c r="CA137" s="31" t="n"/>
+      <c r="CB137" s="24" t="n"/>
+      <c r="CC137" s="24" t="n"/>
+      <c r="CD137" s="24" t="n"/>
+      <c r="CE137" s="24" t="n"/>
+      <c r="CF137" s="24" t="n"/>
+      <c r="CG137" s="24" t="n"/>
+      <c r="CH137" s="24" t="n"/>
+      <c r="CI137" s="24" t="n"/>
+      <c r="CJ137" s="24" t="n"/>
+      <c r="CK137" s="24" t="n"/>
+      <c r="CL137" s="24" t="n"/>
+      <c r="CM137" s="24" t="n"/>
+      <c r="CN137" s="24" t="n"/>
+      <c r="CO137" s="24" t="n"/>
+      <c r="CP137" s="24" t="n"/>
+      <c r="CQ137" s="24" t="n"/>
+      <c r="CR137" s="24" t="n"/>
+      <c r="CS137" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT137" s="24" t="n"/>
+      <c r="CU137" s="24" t="n"/>
+      <c r="CV137" s="24" t="n"/>
+      <c r="CW137" s="24" t="n"/>
+      <c r="CX137" s="24" t="n"/>
+      <c r="CY137" s="24" t="n"/>
+      <c r="CZ137" s="24" t="n"/>
+      <c r="DA137" s="24" t="n"/>
+      <c r="DB137" s="24" t="n"/>
+      <c r="DC137" s="24" t="n"/>
+      <c r="DD137" s="24" t="n"/>
+      <c r="DE137" s="24" t="n"/>
+      <c r="DF137" s="24" t="n"/>
+      <c r="DG137" s="24" t="n"/>
+      <c r="DH137" s="24" t="n"/>
+      <c r="DI137" s="24" t="n"/>
+      <c r="DJ137" s="24" t="n"/>
+      <c r="DK137" s="24" t="n"/>
+      <c r="DL137" s="24" t="n"/>
+      <c r="DM137" s="24" t="n"/>
+      <c r="DN137" s="24" t="n"/>
+      <c r="DO137" s="24" t="n"/>
+      <c r="DP137" s="24" t="n"/>
+      <c r="DQ137" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "52a745e24a739f7876c425755afd5d949b082851299aad8a723cad3af868096f", "away_team": "Hiroshima Carp", "draw_settlement_value": 0.5, "event_id": "142741", "event_start_utc": "2026-10-07T09:00:00Z", "features": {"away_elo": 1450.602544, "base_tie_rate": 0.02376426, "home_advantage": 35.0, "home_elo": 1528.205664}, "historical_source_observation_times_verified": false, "home_team": "Hanshin Tigers", "inference_inputs": {"away_id": "C", "base_tie_rate": 0.02376426, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"C": 1450.602544, "T": 1528.205664}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "f345eb917316d2e897f62c1cdd0f73153115c65da54c30c6137ad76bb7b27869"}, "home_id": "T", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-06T22:24:50.368130+00:00", "outcome_probabilities": {"away": 0.33523569757097316, "draw": 0.02376426, "home": 0.6410000424290269}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.347118, "home": 0.652882}, "snapshot_hash": "18ad0541cfa33136696305362d5830825eab9db052c43c2c564477afb450c425", "sport": "NPB"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/sports/npb/gated.xlsx
+++ b/data/sports/npb/gated.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ137" headerRowCount="1">
-  <autoFilter ref="A1:DQ137"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ143" headerRowCount="1">
+  <autoFilter ref="A1:DQ143"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$137)</f>
+        <f>COUNTA('Picks'!$A$2:$A$143)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$137,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$143,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$137,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$143,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"win")+COUNTIFS('Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"win")+COUNTIFS('Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$137,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$143,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"win")/(COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"win")+COUNTIFS('Picks'!$BX$2:$BX$137,"&gt;0",'Picks'!$V$2:$V$137,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"win")/(COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"win")+COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$137)/SUM('Picks'!$BX$2:$BX$137),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$143)/SUM('Picks'!$BX$2:$BX$143),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$137)</f>
+        <f>SUM('Picks'!$BY$2:$BY$143)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$137,"&lt;&gt;",'Picks'!$AB$2:$AB$137),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$143,"&lt;&gt;",'Picks'!$AB$2:$AB$143),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$137,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$137,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$143,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$143,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$137,'Picks'!$AM$2:$AM$137,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$143,'Picks'!$AM$2:$AM$143,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$137,$A14,'Picks'!$U$2:$U$137,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$143,$A14,'Picks'!$U$2:$U$143,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$137,$A14,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$143,$A14,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$137,$A14,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$143,$A14,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$137,'Picks'!$H$2:$H$137,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$143,'Picks'!$H$2:$H$143,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$137,'Picks'!$H$2:$H$137,$A14,'Picks'!$U$2:$U$137,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$143,'Picks'!$H$2:$H$143,$A14,'Picks'!$U$2:$U$143,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$137,$A15,'Picks'!$U$2:$U$137,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$143,$A15,'Picks'!$U$2:$U$143,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$137,$A15,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$143,$A15,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$137,$A15,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$143,$A15,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$137,'Picks'!$H$2:$H$137,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$143,'Picks'!$H$2:$H$143,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$137,'Picks'!$H$2:$H$137,$A15,'Picks'!$U$2:$U$137,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$143,'Picks'!$H$2:$H$143,$A15,'Picks'!$U$2:$U$143,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$137,$A16,'Picks'!$U$2:$U$137,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$143,$A16,'Picks'!$U$2:$U$143,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$137,$A16,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$143,$A16,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$137,$A16,'Picks'!$U$2:$U$137,"settled",'Picks'!$V$2:$V$137,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$143,$A16,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$137,'Picks'!$H$2:$H$137,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$143,'Picks'!$H$2:$H$143,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$137,'Picks'!$H$2:$H$137,$A16,'Picks'!$U$2:$U$137,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$143,'Picks'!$H$2:$H$143,$A16,'Picks'!$U$2:$U$143,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ137"/>
+  <dimension ref="A1:DQ143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -44615,12 +44615,12 @@
     <row r="137" ht="36" customHeight="1">
       <c r="A137" s="24" t="inlineStr">
         <is>
-          <t>60a44c11dca244c0</t>
+          <t>0c02d5d605be4adb</t>
         </is>
       </c>
       <c r="B137" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:24:50.453102Z</t>
+          <t>2026-10-07T05:28:32.825150Z</t>
         </is>
       </c>
       <c r="C137" s="24" t="inlineStr">
@@ -44665,23 +44665,23 @@
         </is>
       </c>
       <c r="L137" s="26" t="n">
-        <v>-156</v>
+        <v>-150</v>
       </c>
       <c r="M137" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.666667</v>
       </c>
       <c r="N137" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.6</v>
       </c>
       <c r="O137" s="28" t="n">
-        <v>0.652882</v>
+        <v>0.6338279999999999</v>
       </c>
       <c r="P137" s="28" t="n"/>
       <c r="Q137" s="28" t="n">
-        <v>0.043507</v>
+        <v>0.033828</v>
       </c>
       <c r="R137" s="26" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="S137" s="29" t="n">
         <v>1</v>
@@ -44693,21 +44693,41 @@
       </c>
       <c r="U137" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V137" s="24" t="n"/>
-      <c r="W137" s="26" t="n"/>
-      <c r="X137" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V137" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W137" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X137" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y137" s="25" t="n"/>
-      <c r="Z137" s="26" t="n"/>
-      <c r="AA137" s="28" t="n"/>
-      <c r="AB137" s="28" t="n"/>
-      <c r="AC137" s="30" t="n"/>
-      <c r="AD137" s="24" t="n"/>
+      <c r="Z137" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="AA137" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB137" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC137" s="30" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AD137" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:05:00.715618Z</t>
+        </is>
+      </c>
       <c r="AE137" s="31" t="inlineStr">
         <is>
-          <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-hta-hci-2026-10-07). Tie probability=0.0238.</t>
+          <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-npb-hta-hci-2026-10-07). Tie probability=0.0239.</t>
         </is>
       </c>
       <c r="AF137" s="31" t="inlineStr">
@@ -44791,7 +44811,7 @@
       </c>
       <c r="BA137" s="24" t="inlineStr">
         <is>
-          <t>52a745e24a739f7876c425755afd5d949b082851299aad8a723cad3af868096f</t>
+          <t>68d07ee48d1509bcf95582a676d54274539f6ebe66c40e274ab6c8ab22373648</t>
         </is>
       </c>
       <c r="BB137" s="24" t="inlineStr">
@@ -44806,7 +44826,7 @@
       </c>
       <c r="BD137" s="24" t="inlineStr">
         <is>
-          <t>52a745e24a739f7876c425755afd5d949b082851299aad8a723cad3af868096f</t>
+          <t>68d07ee48d1509bcf95582a676d54274539f6ebe66c40e274ab6c8ab22373648</t>
         </is>
       </c>
       <c r="BE137" s="24" t="inlineStr">
@@ -44826,7 +44846,7 @@
       </c>
       <c r="BH137" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:24:50.452100Z</t>
+          <t>2026-10-07T05:28:32.825150Z</t>
         </is>
       </c>
       <c r="BI137" s="24" t="inlineStr">
@@ -44836,19 +44856,23 @@
       </c>
       <c r="BJ137" s="25" t="n"/>
       <c r="BK137" s="26" t="n">
-        <v>-156</v>
+        <v>-150</v>
       </c>
       <c r="BL137" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.666667</v>
       </c>
       <c r="BM137" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.6</v>
       </c>
       <c r="BN137" s="28" t="n"/>
       <c r="BO137" s="28" t="n"/>
       <c r="BP137" s="25" t="n"/>
-      <c r="BQ137" s="27" t="n"/>
-      <c r="BR137" s="28" t="n"/>
+      <c r="BQ137" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BR137" s="28" t="n">
+        <v>0.6</v>
+      </c>
       <c r="BS137" s="28" t="n"/>
       <c r="BT137" s="28" t="n"/>
       <c r="BU137" s="25" t="n"/>
@@ -44905,7 +44929,1845 @@
       <c r="DP137" s="24" t="n"/>
       <c r="DQ137" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "52a745e24a739f7876c425755afd5d949b082851299aad8a723cad3af868096f", "away_team": "Hiroshima Carp", "draw_settlement_value": 0.5, "event_id": "142741", "event_start_utc": "2026-10-07T09:00:00Z", "features": {"away_elo": 1450.602544, "base_tie_rate": 0.02376426, "home_advantage": 35.0, "home_elo": 1528.205664}, "historical_source_observation_times_verified": false, "home_team": "Hanshin Tigers", "inference_inputs": {"away_id": "C", "base_tie_rate": 0.02376426, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"C": 1450.602544, "T": 1528.205664}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "f345eb917316d2e897f62c1cdd0f73153115c65da54c30c6137ad76bb7b27869"}, "home_id": "T", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-06T22:24:50.368130+00:00", "outcome_probabilities": {"away": 0.33523569757097316, "draw": 0.02376426, "home": 0.6410000424290269}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.347118, "home": 0.652882}, "snapshot_hash": "18ad0541cfa33136696305362d5830825eab9db052c43c2c564477afb450c425", "sport": "NPB"}</t>
+          <t>{"artifact_hash": "68d07ee48d1509bcf95582a676d54274539f6ebe66c40e274ab6c8ab22373648", "away_team": "Hiroshima Carp", "draw_settlement_value": 0.5, "event_id": "142741", "event_start_utc": "2026-10-07T09:00:00Z", "features": {"away_elo": 1459.619403, "base_tie_rate": 0.02389967, "home_advantage": 35.0, "home_elo": 1522.390934}, "historical_source_observation_times_verified": false, "home_team": "Hanshin Tigers", "inference_inputs": {"away_id": "C", "base_tie_rate": 0.02389967, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"C": 1459.619403, "T": 1522.390934}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "58ea522476e21dc70a719fe60647c19a772fcb4703fef8ed2d47c4ba7f07c2d5"}, "home_id": "T", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-07T05:28:32.688023+00:00", "outcome_probabilities": {"away": 0.35422255357395394, "draw": 0.02389967, "home": 0.621877776426046}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.366172, "home": 0.633828}, "snapshot_hash": "87cf5b46fdc98e6724511cbd171f17824be2c7e42a1ccf8425aebafdb60d7db5", "sport": "NPB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="36" customHeight="1">
+      <c r="A138" s="24" t="inlineStr">
+        <is>
+          <t>a2e16e96b39c44c5</t>
+        </is>
+      </c>
+      <c r="B138" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:27:05.714336Z</t>
+        </is>
+      </c>
+      <c r="C138" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D138" s="24" t="inlineStr">
+        <is>
+          <t>144497</t>
+        </is>
+      </c>
+      <c r="E138" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F138" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="G138" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="H138" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I138" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J138" s="25" t="n"/>
+      <c r="K138" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L138" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M138" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N138" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O138" s="28" t="n">
+        <v>0.691636</v>
+      </c>
+      <c r="P138" s="28" t="n"/>
+      <c r="Q138" s="28" t="n">
+        <v>0.051348</v>
+      </c>
+      <c r="R138" s="26" t="n">
+        <v>46</v>
+      </c>
+      <c r="S138" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T138" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U138" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V138" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W138" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X138" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y138" s="25" t="n"/>
+      <c r="Z138" s="26" t="n"/>
+      <c r="AA138" s="28" t="n"/>
+      <c r="AB138" s="28" t="n"/>
+      <c r="AC138" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD138" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T04:38:15.464193Z</t>
+        </is>
+      </c>
+      <c r="AE138" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6400 (market_slug=aec-npb-hta-tys-2026-10-08). Tie probability=0.0239.</t>
+        </is>
+      </c>
+      <c r="AF138" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG138" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH138" s="24" t="n"/>
+      <c r="AI138" s="31" t="n"/>
+      <c r="AJ138" s="31" t="n"/>
+      <c r="AK138" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL138" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM138" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN138" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO138" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP138" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AQ138" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AR138" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AS138" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AT138" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AU138" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AV138" s="24" t="n"/>
+      <c r="AW138" s="24" t="n"/>
+      <c r="AX138" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY138" s="24" t="n"/>
+      <c r="AZ138" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA138" s="24" t="inlineStr">
+        <is>
+          <t>b308d622b430a23c8c792fdf24eacf1319adf7cdec74fedf9555576e3842e388</t>
+        </is>
+      </c>
+      <c r="BB138" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC138" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD138" s="24" t="inlineStr">
+        <is>
+          <t>b308d622b430a23c8c792fdf24eacf1319adf7cdec74fedf9555576e3842e388</t>
+        </is>
+      </c>
+      <c r="BE138" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF138" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG138" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH138" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:27:05.714336Z</t>
+        </is>
+      </c>
+      <c r="BI138" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ138" s="25" t="n"/>
+      <c r="BK138" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL138" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM138" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN138" s="28" t="n"/>
+      <c r="BO138" s="28" t="n"/>
+      <c r="BP138" s="25" t="n"/>
+      <c r="BQ138" s="27" t="n"/>
+      <c r="BR138" s="28" t="n"/>
+      <c r="BS138" s="28" t="n"/>
+      <c r="BT138" s="28" t="n"/>
+      <c r="BU138" s="25" t="n"/>
+      <c r="BV138" s="29" t="n"/>
+      <c r="BW138" s="24" t="n"/>
+      <c r="BX138" s="30" t="n"/>
+      <c r="BY138" s="27" t="n"/>
+      <c r="BZ138" s="24" t="n"/>
+      <c r="CA138" s="31" t="n"/>
+      <c r="CB138" s="24" t="n"/>
+      <c r="CC138" s="24" t="n"/>
+      <c r="CD138" s="24" t="n"/>
+      <c r="CE138" s="24" t="n"/>
+      <c r="CF138" s="24" t="n"/>
+      <c r="CG138" s="24" t="n"/>
+      <c r="CH138" s="24" t="n"/>
+      <c r="CI138" s="24" t="n"/>
+      <c r="CJ138" s="24" t="n"/>
+      <c r="CK138" s="24" t="n"/>
+      <c r="CL138" s="24" t="n"/>
+      <c r="CM138" s="24" t="n"/>
+      <c r="CN138" s="24" t="n"/>
+      <c r="CO138" s="24" t="n"/>
+      <c r="CP138" s="24" t="n"/>
+      <c r="CQ138" s="24" t="n"/>
+      <c r="CR138" s="24" t="n"/>
+      <c r="CS138" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT138" s="24" t="n"/>
+      <c r="CU138" s="24" t="n"/>
+      <c r="CV138" s="24" t="n"/>
+      <c r="CW138" s="24" t="n"/>
+      <c r="CX138" s="24" t="n"/>
+      <c r="CY138" s="24" t="n"/>
+      <c r="CZ138" s="24" t="n"/>
+      <c r="DA138" s="24" t="n"/>
+      <c r="DB138" s="24" t="n"/>
+      <c r="DC138" s="24" t="n"/>
+      <c r="DD138" s="24" t="n"/>
+      <c r="DE138" s="24" t="n"/>
+      <c r="DF138" s="24" t="n"/>
+      <c r="DG138" s="24" t="n"/>
+      <c r="DH138" s="24" t="n"/>
+      <c r="DI138" s="24" t="n"/>
+      <c r="DJ138" s="24" t="n"/>
+      <c r="DK138" s="24" t="n"/>
+      <c r="DL138" s="24" t="n"/>
+      <c r="DM138" s="24" t="n"/>
+      <c r="DN138" s="24" t="n"/>
+      <c r="DO138" s="24" t="n"/>
+      <c r="DP138" s="24" t="n"/>
+      <c r="DQ138" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "b308d622b430a23c8c792fdf24eacf1319adf7cdec74fedf9555576e3842e388", "away_team": "Tokyo Yakult Swallows", "draw_settlement_value": 0.5, "event_id": "144497", "event_start_utc": "2026-10-08T09:00:00Z", "features": {"away_elo": 1416.131229, "base_tie_rate": 0.02389401, "home_advantage": 35.0, "home_elo": 1525.294099}, "historical_source_observation_times_verified": false, "home_team": "Hanshin Tigers", "inference_inputs": {"away_id": "S", "base_tie_rate": 0.02389401, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"S": 1416.131229, "T": 1525.294099}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "58ea522476e21dc70a719fe60647c19a772fcb4703fef8ed2d47c4ba7f07c2d5"}, "home_id": "T", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-07T22:27:05.633273+00:00", "outcome_probabilities": {"away": 0.2964169774262092, "draw": 0.02389401, "home": 0.6796890125737908}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.308364, "home": 0.691636}, "snapshot_hash": "f1fb387be0a94b9f162bcc3cdfb4c43a15c021a242d22a9829b2d01dd32a68d8", "sport": "NPB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="36" customHeight="1">
+      <c r="A139" s="24" t="inlineStr">
+        <is>
+          <t>508583b32a8149f4</t>
+        </is>
+      </c>
+      <c r="B139" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T01:06:46.457952Z</t>
+        </is>
+      </c>
+      <c r="C139" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D139" s="24" t="inlineStr">
+        <is>
+          <t>148643</t>
+        </is>
+      </c>
+      <c r="E139" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F139" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="G139" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="H139" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I139" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J139" s="25" t="n"/>
+      <c r="K139" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L139" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M139" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N139" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="O139" s="28" t="n">
+        <v>0.537178</v>
+      </c>
+      <c r="P139" s="28" t="n"/>
+      <c r="Q139" s="28" t="n">
+        <v>0.067694</v>
+      </c>
+      <c r="R139" s="26" t="n">
+        <v>54</v>
+      </c>
+      <c r="S139" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T139" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U139" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V139" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W139" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X139" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y139" s="25" t="n"/>
+      <c r="Z139" s="26" t="n"/>
+      <c r="AA139" s="28" t="n"/>
+      <c r="AB139" s="28" t="n"/>
+      <c r="AC139" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD139" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T22:02:29.998891Z</t>
+        </is>
+      </c>
+      <c r="AE139" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4700 (market_slug=aec-npb-ssl-nhf-2026-10-11). Tie probability=0.0239.</t>
+        </is>
+      </c>
+      <c r="AF139" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG139" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH139" s="24" t="n"/>
+      <c r="AI139" s="31" t="n"/>
+      <c r="AJ139" s="31" t="n"/>
+      <c r="AK139" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL139" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM139" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN139" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO139" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP139" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AQ139" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AR139" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AS139" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AT139" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AU139" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AV139" s="24" t="n"/>
+      <c r="AW139" s="24" t="n"/>
+      <c r="AX139" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY139" s="24" t="n"/>
+      <c r="AZ139" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA139" s="24" t="inlineStr">
+        <is>
+          <t>893602d01e5e033b555535a8754105d97c348185ccc30e37513b1c524c69ad79</t>
+        </is>
+      </c>
+      <c r="BB139" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC139" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD139" s="24" t="inlineStr">
+        <is>
+          <t>893602d01e5e033b555535a8754105d97c348185ccc30e37513b1c524c69ad79</t>
+        </is>
+      </c>
+      <c r="BE139" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF139" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG139" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH139" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T01:06:46.403224Z</t>
+        </is>
+      </c>
+      <c r="BI139" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ139" s="25" t="n"/>
+      <c r="BK139" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="BL139" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM139" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="BN139" s="28" t="n"/>
+      <c r="BO139" s="28" t="n"/>
+      <c r="BP139" s="25" t="n"/>
+      <c r="BQ139" s="27" t="n"/>
+      <c r="BR139" s="28" t="n"/>
+      <c r="BS139" s="28" t="n"/>
+      <c r="BT139" s="28" t="n"/>
+      <c r="BU139" s="25" t="n"/>
+      <c r="BV139" s="29" t="n"/>
+      <c r="BW139" s="24" t="n"/>
+      <c r="BX139" s="30" t="n"/>
+      <c r="BY139" s="27" t="n"/>
+      <c r="BZ139" s="24" t="n"/>
+      <c r="CA139" s="31" t="n"/>
+      <c r="CB139" s="24" t="n"/>
+      <c r="CC139" s="24" t="n"/>
+      <c r="CD139" s="24" t="n"/>
+      <c r="CE139" s="24" t="n"/>
+      <c r="CF139" s="24" t="n"/>
+      <c r="CG139" s="24" t="n"/>
+      <c r="CH139" s="24" t="n"/>
+      <c r="CI139" s="24" t="n"/>
+      <c r="CJ139" s="24" t="n"/>
+      <c r="CK139" s="24" t="n"/>
+      <c r="CL139" s="24" t="n"/>
+      <c r="CM139" s="24" t="n"/>
+      <c r="CN139" s="24" t="n"/>
+      <c r="CO139" s="24" t="n"/>
+      <c r="CP139" s="24" t="n"/>
+      <c r="CQ139" s="24" t="n"/>
+      <c r="CR139" s="24" t="n"/>
+      <c r="CS139" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT139" s="24" t="n"/>
+      <c r="CU139" s="24" t="n"/>
+      <c r="CV139" s="24" t="n"/>
+      <c r="CW139" s="24" t="n"/>
+      <c r="CX139" s="24" t="n"/>
+      <c r="CY139" s="24" t="n"/>
+      <c r="CZ139" s="24" t="n"/>
+      <c r="DA139" s="24" t="n"/>
+      <c r="DB139" s="24" t="n"/>
+      <c r="DC139" s="24" t="n"/>
+      <c r="DD139" s="24" t="n"/>
+      <c r="DE139" s="24" t="n"/>
+      <c r="DF139" s="24" t="n"/>
+      <c r="DG139" s="24" t="n"/>
+      <c r="DH139" s="24" t="n"/>
+      <c r="DI139" s="24" t="n"/>
+      <c r="DJ139" s="24" t="n"/>
+      <c r="DK139" s="24" t="n"/>
+      <c r="DL139" s="24" t="n"/>
+      <c r="DM139" s="24" t="n"/>
+      <c r="DN139" s="24" t="n"/>
+      <c r="DO139" s="24" t="n"/>
+      <c r="DP139" s="24" t="n"/>
+      <c r="DQ139" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "893602d01e5e033b555535a8754105d97c348185ccc30e37513b1c524c69ad79", "away_team": "Nippon Ham Fighters", "draw_settlement_value": 0.5, "event_id": "148643", "event_start_utc": "2026-10-11T05:00:00Z", "features": {"away_elo": 1551.787498, "base_tie_rate": 0.02387707, "home_advantage": 35.0, "home_elo": 1543.304526}, "historical_source_observation_times_verified": false, "home_team": "Saitama Seibu Lions", "inference_inputs": {"away_id": "F", "base_tie_rate": 0.02387707, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"F": 1551.787498, "L": 1543.304526}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "L", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-11T01:06:46.340498+00:00", "outcome_probabilities": {"away": 0.450883728309193, "draw": 0.02387707, "home": 0.5252392016908071}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.462822, "home": 0.537178}, "snapshot_hash": "0adfb8530cd4d68cabea01e26674e27f24c99521898581e14f4074d3b0b3e9fe", "sport": "NPB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="36" customHeight="1">
+      <c r="A140" s="24" t="inlineStr">
+        <is>
+          <t>34002f6d4c144633</t>
+        </is>
+      </c>
+      <c r="B140" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T01:06:46.457952Z</t>
+        </is>
+      </c>
+      <c r="C140" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D140" s="24" t="inlineStr">
+        <is>
+          <t>148644</t>
+        </is>
+      </c>
+      <c r="E140" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F140" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="G140" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="H140" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I140" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J140" s="25" t="n"/>
+      <c r="K140" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L140" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M140" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N140" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O140" s="28" t="n">
+        <v>0.525257</v>
+      </c>
+      <c r="P140" s="28" t="n"/>
+      <c r="Q140" s="28" t="n">
+        <v>0.035061</v>
+      </c>
+      <c r="R140" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="S140" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T140" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U140" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V140" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W140" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X140" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y140" s="25" t="n"/>
+      <c r="Z140" s="26" t="n"/>
+      <c r="AA140" s="28" t="n"/>
+      <c r="AB140" s="28" t="n"/>
+      <c r="AC140" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD140" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T22:02:31.140301Z</t>
+        </is>
+      </c>
+      <c r="AE140" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4900 (market_slug=aec-npb-ygo-ybo-2026-10-11). Tie probability=0.0239.</t>
+        </is>
+      </c>
+      <c r="AF140" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG140" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH140" s="24" t="n"/>
+      <c r="AI140" s="31" t="n"/>
+      <c r="AJ140" s="31" t="n"/>
+      <c r="AK140" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL140" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM140" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN140" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO140" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP140" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AQ140" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AR140" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AS140" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AT140" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AU140" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AV140" s="24" t="n"/>
+      <c r="AW140" s="24" t="n"/>
+      <c r="AX140" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY140" s="24" t="n"/>
+      <c r="AZ140" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA140" s="24" t="inlineStr">
+        <is>
+          <t>893602d01e5e033b555535a8754105d97c348185ccc30e37513b1c524c69ad79</t>
+        </is>
+      </c>
+      <c r="BB140" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC140" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD140" s="24" t="inlineStr">
+        <is>
+          <t>893602d01e5e033b555535a8754105d97c348185ccc30e37513b1c524c69ad79</t>
+        </is>
+      </c>
+      <c r="BE140" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF140" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG140" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH140" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T01:06:46.457952Z</t>
+        </is>
+      </c>
+      <c r="BI140" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ140" s="25" t="n"/>
+      <c r="BK140" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL140" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM140" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN140" s="28" t="n"/>
+      <c r="BO140" s="28" t="n"/>
+      <c r="BP140" s="25" t="n"/>
+      <c r="BQ140" s="27" t="n"/>
+      <c r="BR140" s="28" t="n"/>
+      <c r="BS140" s="28" t="n"/>
+      <c r="BT140" s="28" t="n"/>
+      <c r="BU140" s="25" t="n"/>
+      <c r="BV140" s="29" t="n"/>
+      <c r="BW140" s="24" t="n"/>
+      <c r="BX140" s="30" t="n"/>
+      <c r="BY140" s="27" t="n"/>
+      <c r="BZ140" s="24" t="n"/>
+      <c r="CA140" s="31" t="n"/>
+      <c r="CB140" s="24" t="n"/>
+      <c r="CC140" s="24" t="n"/>
+      <c r="CD140" s="24" t="n"/>
+      <c r="CE140" s="24" t="n"/>
+      <c r="CF140" s="24" t="n"/>
+      <c r="CG140" s="24" t="n"/>
+      <c r="CH140" s="24" t="n"/>
+      <c r="CI140" s="24" t="n"/>
+      <c r="CJ140" s="24" t="n"/>
+      <c r="CK140" s="24" t="n"/>
+      <c r="CL140" s="24" t="n"/>
+      <c r="CM140" s="24" t="n"/>
+      <c r="CN140" s="24" t="n"/>
+      <c r="CO140" s="24" t="n"/>
+      <c r="CP140" s="24" t="n"/>
+      <c r="CQ140" s="24" t="n"/>
+      <c r="CR140" s="24" t="n"/>
+      <c r="CS140" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT140" s="24" t="n"/>
+      <c r="CU140" s="24" t="n"/>
+      <c r="CV140" s="24" t="n"/>
+      <c r="CW140" s="24" t="n"/>
+      <c r="CX140" s="24" t="n"/>
+      <c r="CY140" s="24" t="n"/>
+      <c r="CZ140" s="24" t="n"/>
+      <c r="DA140" s="24" t="n"/>
+      <c r="DB140" s="24" t="n"/>
+      <c r="DC140" s="24" t="n"/>
+      <c r="DD140" s="24" t="n"/>
+      <c r="DE140" s="24" t="n"/>
+      <c r="DF140" s="24" t="n"/>
+      <c r="DG140" s="24" t="n"/>
+      <c r="DH140" s="24" t="n"/>
+      <c r="DI140" s="24" t="n"/>
+      <c r="DJ140" s="24" t="n"/>
+      <c r="DK140" s="24" t="n"/>
+      <c r="DL140" s="24" t="n"/>
+      <c r="DM140" s="24" t="n"/>
+      <c r="DN140" s="24" t="n"/>
+      <c r="DO140" s="24" t="n"/>
+      <c r="DP140" s="24" t="n"/>
+      <c r="DQ140" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "893602d01e5e033b555535a8754105d97c348185ccc30e37513b1c524c69ad79", "away_team": "Yokohama BayStars", "draw_settlement_value": 0.5, "event_id": "148644", "event_start_utc": "2026-10-11T05:00:00Z", "features": {"away_elo": 1516.853935, "base_tie_rate": 0.02387707, "home_advantage": 35.0, "home_elo": 1499.849559}, "historical_source_observation_times_verified": false, "home_team": "Yomiuri Giants", "inference_inputs": {"away_id": "DB", "base_tie_rate": 0.02387707, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"DB": 1516.853935, "G": 1499.849559}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "G", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-11T01:06:46.340498+00:00", "outcome_probabilities": {"away": 0.4628046256439446, "draw": 0.02387707, "home": 0.5133183043560555}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.474743, "home": 0.525257}, "snapshot_hash": "3b835560ef63bf24f261f0734a60c05f92b317cc06babf16f710ccdfe5a46891", "sport": "NPB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="36" customHeight="1">
+      <c r="A141" s="24" t="inlineStr">
+        <is>
+          <t>2c1dbf3872eb4972</t>
+        </is>
+      </c>
+      <c r="B141" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T22:38:31.027034Z</t>
+        </is>
+      </c>
+      <c r="C141" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D141" s="24" t="inlineStr">
+        <is>
+          <t>154782</t>
+        </is>
+      </c>
+      <c r="E141" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F141" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="G141" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="H141" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I141" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J141" s="25" t="n"/>
+      <c r="K141" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L141" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M141" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N141" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O141" s="28" t="n">
+        <v>0.525134</v>
+      </c>
+      <c r="P141" s="28" t="n"/>
+      <c r="Q141" s="28" t="n">
+        <v>-0.014037</v>
+      </c>
+      <c r="R141" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="S141" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T141" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U141" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V141" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W141" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X141" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y141" s="25" t="n"/>
+      <c r="Z141" s="26" t="n"/>
+      <c r="AA141" s="28" t="n"/>
+      <c r="AB141" s="28" t="n"/>
+      <c r="AC141" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD141" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T22:03:55.470396Z</t>
+        </is>
+      </c>
+      <c r="AE141" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5400 (market_slug=aec-npb-ssl-nhf-2026-10-12). Tie probability=0.0239.</t>
+        </is>
+      </c>
+      <c r="AF141" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG141" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH141" s="24" t="n"/>
+      <c r="AI141" s="31" t="n"/>
+      <c r="AJ141" s="31" t="n"/>
+      <c r="AK141" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL141" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM141" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN141" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO141" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP141" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AQ141" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AR141" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AS141" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AT141" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AU141" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AV141" s="24" t="n"/>
+      <c r="AW141" s="24" t="n"/>
+      <c r="AX141" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY141" s="24" t="n"/>
+      <c r="AZ141" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA141" s="24" t="inlineStr">
+        <is>
+          <t>b1442f66b73b82e842e6c57616754b46017f10f0e356edc8600ad4d6610cda2f</t>
+        </is>
+      </c>
+      <c r="BB141" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC141" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD141" s="24" t="inlineStr">
+        <is>
+          <t>b1442f66b73b82e842e6c57616754b46017f10f0e356edc8600ad4d6610cda2f</t>
+        </is>
+      </c>
+      <c r="BE141" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF141" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG141" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH141" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T22:38:31.026029Z</t>
+        </is>
+      </c>
+      <c r="BI141" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ141" s="25" t="n"/>
+      <c r="BK141" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL141" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM141" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN141" s="28" t="n"/>
+      <c r="BO141" s="28" t="n"/>
+      <c r="BP141" s="25" t="n"/>
+      <c r="BQ141" s="27" t="n"/>
+      <c r="BR141" s="28" t="n"/>
+      <c r="BS141" s="28" t="n"/>
+      <c r="BT141" s="28" t="n"/>
+      <c r="BU141" s="25" t="n"/>
+      <c r="BV141" s="29" t="n"/>
+      <c r="BW141" s="24" t="n"/>
+      <c r="BX141" s="30" t="n"/>
+      <c r="BY141" s="27" t="n"/>
+      <c r="BZ141" s="24" t="n"/>
+      <c r="CA141" s="31" t="n"/>
+      <c r="CB141" s="24" t="n"/>
+      <c r="CC141" s="24" t="n"/>
+      <c r="CD141" s="24" t="n"/>
+      <c r="CE141" s="24" t="n"/>
+      <c r="CF141" s="24" t="n"/>
+      <c r="CG141" s="24" t="n"/>
+      <c r="CH141" s="24" t="n"/>
+      <c r="CI141" s="24" t="n"/>
+      <c r="CJ141" s="24" t="n"/>
+      <c r="CK141" s="24" t="n"/>
+      <c r="CL141" s="24" t="n"/>
+      <c r="CM141" s="24" t="n"/>
+      <c r="CN141" s="24" t="n"/>
+      <c r="CO141" s="24" t="n"/>
+      <c r="CP141" s="24" t="n"/>
+      <c r="CQ141" s="24" t="n"/>
+      <c r="CR141" s="24" t="n"/>
+      <c r="CS141" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT141" s="24" t="n"/>
+      <c r="CU141" s="24" t="n"/>
+      <c r="CV141" s="24" t="n"/>
+      <c r="CW141" s="24" t="n"/>
+      <c r="CX141" s="24" t="n"/>
+      <c r="CY141" s="24" t="n"/>
+      <c r="CZ141" s="24" t="n"/>
+      <c r="DA141" s="24" t="n"/>
+      <c r="DB141" s="24" t="n"/>
+      <c r="DC141" s="24" t="n"/>
+      <c r="DD141" s="24" t="n"/>
+      <c r="DE141" s="24" t="n"/>
+      <c r="DF141" s="24" t="n"/>
+      <c r="DG141" s="24" t="n"/>
+      <c r="DH141" s="24" t="n"/>
+      <c r="DI141" s="24" t="n"/>
+      <c r="DJ141" s="24" t="n"/>
+      <c r="DK141" s="24" t="n"/>
+      <c r="DL141" s="24" t="n"/>
+      <c r="DM141" s="24" t="n"/>
+      <c r="DN141" s="24" t="n"/>
+      <c r="DO141" s="24" t="n"/>
+      <c r="DP141" s="24" t="n"/>
+      <c r="DQ141" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "b1442f66b73b82e842e6c57616754b46017f10f0e356edc8600ad4d6610cda2f", "away_team": "Nippon Ham Fighters", "draw_settlement_value": 0.5, "event_id": "154782", "event_start_utc": "2026-10-12T05:00:00Z", "features": {"away_elo": 1556.092195, "base_tie_rate": 0.02386578, "home_advantage": 35.0, "home_elo": 1538.999828}, "historical_source_observation_times_verified": false, "home_team": "Saitama Seibu Lions", "inference_inputs": {"away_id": "F", "base_tie_rate": 0.02386578, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"F": 1556.092195, "L": 1538.999828}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "L", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-11T22:38:26.630105+00:00", "outcome_probabilities": {"away": 0.46293325623630444, "draw": 0.02386578, "home": 0.5132009637636956}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.474866, "home": 0.525134}, "snapshot_hash": "e7ed6afe98bfebdb9e5fb4b2aaaee8218eb1507832c8782d3e4baa9d3c420c27", "sport": "NPB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="36" customHeight="1">
+      <c r="A142" s="24" t="inlineStr">
+        <is>
+          <t>bf57d1ea8d5a41ac</t>
+        </is>
+      </c>
+      <c r="B142" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:28:52.203222Z</t>
+        </is>
+      </c>
+      <c r="C142" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D142" s="24" t="inlineStr">
+        <is>
+          <t>154783</t>
+        </is>
+      </c>
+      <c r="E142" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F142" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="G142" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="H142" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I142" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J142" s="25" t="n"/>
+      <c r="K142" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L142" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M142" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N142" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O142" s="28" t="n">
+        <v>0.547141</v>
+      </c>
+      <c r="P142" s="28" t="n"/>
+      <c r="Q142" s="28" t="n">
+        <v>-0.052859</v>
+      </c>
+      <c r="R142" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T142" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U142" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V142" s="24" t="n"/>
+      <c r="W142" s="26" t="n"/>
+      <c r="X142" s="26" t="n"/>
+      <c r="Y142" s="25" t="n"/>
+      <c r="Z142" s="26" t="n"/>
+      <c r="AA142" s="28" t="n"/>
+      <c r="AB142" s="28" t="n"/>
+      <c r="AC142" s="30" t="n"/>
+      <c r="AD142" s="24" t="n"/>
+      <c r="AE142" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-npb-hta-ybo-2026-10-14). Tie probability=0.0239.</t>
+        </is>
+      </c>
+      <c r="AF142" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG142" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH142" s="24" t="n"/>
+      <c r="AI142" s="31" t="n"/>
+      <c r="AJ142" s="31" t="n"/>
+      <c r="AK142" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL142" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM142" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN142" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO142" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP142" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AQ142" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AR142" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AS142" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AT142" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AU142" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AV142" s="24" t="n"/>
+      <c r="AW142" s="24" t="n"/>
+      <c r="AX142" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY142" s="24" t="n"/>
+      <c r="AZ142" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA142" s="24" t="inlineStr">
+        <is>
+          <t>22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7</t>
+        </is>
+      </c>
+      <c r="BB142" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC142" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD142" s="24" t="inlineStr">
+        <is>
+          <t>22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7</t>
+        </is>
+      </c>
+      <c r="BE142" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF142" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG142" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH142" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:28:51.878028Z</t>
+        </is>
+      </c>
+      <c r="BI142" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ142" s="25" t="n"/>
+      <c r="BK142" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL142" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM142" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN142" s="28" t="n"/>
+      <c r="BO142" s="28" t="n"/>
+      <c r="BP142" s="25" t="n"/>
+      <c r="BQ142" s="27" t="n"/>
+      <c r="BR142" s="28" t="n"/>
+      <c r="BS142" s="28" t="n"/>
+      <c r="BT142" s="28" t="n"/>
+      <c r="BU142" s="25" t="n"/>
+      <c r="BV142" s="29" t="n"/>
+      <c r="BW142" s="24" t="n"/>
+      <c r="BX142" s="30" t="n"/>
+      <c r="BY142" s="27" t="n"/>
+      <c r="BZ142" s="24" t="n"/>
+      <c r="CA142" s="31" t="n"/>
+      <c r="CB142" s="24" t="n"/>
+      <c r="CC142" s="24" t="n"/>
+      <c r="CD142" s="24" t="n"/>
+      <c r="CE142" s="24" t="n"/>
+      <c r="CF142" s="24" t="n"/>
+      <c r="CG142" s="24" t="n"/>
+      <c r="CH142" s="24" t="n"/>
+      <c r="CI142" s="24" t="n"/>
+      <c r="CJ142" s="24" t="n"/>
+      <c r="CK142" s="24" t="n"/>
+      <c r="CL142" s="24" t="n"/>
+      <c r="CM142" s="24" t="n"/>
+      <c r="CN142" s="24" t="n"/>
+      <c r="CO142" s="24" t="n"/>
+      <c r="CP142" s="24" t="n"/>
+      <c r="CQ142" s="24" t="n"/>
+      <c r="CR142" s="24" t="n"/>
+      <c r="CS142" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT142" s="24" t="n"/>
+      <c r="CU142" s="24" t="n"/>
+      <c r="CV142" s="24" t="n"/>
+      <c r="CW142" s="24" t="n"/>
+      <c r="CX142" s="24" t="n"/>
+      <c r="CY142" s="24" t="n"/>
+      <c r="CZ142" s="24" t="n"/>
+      <c r="DA142" s="24" t="n"/>
+      <c r="DB142" s="24" t="n"/>
+      <c r="DC142" s="24" t="n"/>
+      <c r="DD142" s="24" t="n"/>
+      <c r="DE142" s="24" t="n"/>
+      <c r="DF142" s="24" t="n"/>
+      <c r="DG142" s="24" t="n"/>
+      <c r="DH142" s="24" t="n"/>
+      <c r="DI142" s="24" t="n"/>
+      <c r="DJ142" s="24" t="n"/>
+      <c r="DK142" s="24" t="n"/>
+      <c r="DL142" s="24" t="n"/>
+      <c r="DM142" s="24" t="n"/>
+      <c r="DN142" s="24" t="n"/>
+      <c r="DO142" s="24" t="n"/>
+      <c r="DP142" s="24" t="n"/>
+      <c r="DQ142" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7", "away_team": "Yokohama BayStars", "draw_settlement_value": 0.5, "event_id": "154783", "event_start_utc": "2026-10-14T09:00:00Z", "features": {"away_elo": 1521.060932, "base_tie_rate": 0.02386015, "home_advantage": 35.0, "home_elo": 1519.723482}, "historical_source_observation_times_verified": false, "home_team": "Hanshin Tigers", "inference_inputs": {"away_id": "DB", "base_tie_rate": 0.02386015, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"DB": 1521.060932, "T": 1519.723482}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "T", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-13T22:28:51.412639+00:00", "outcome_probabilities": {"away": 0.4409289279790772, "draw": 0.02386015, "home": 0.5352109220209229}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.452859, "home": 0.547141}, "snapshot_hash": "7015e4880439a4d4afc64cf919c0221dc4d3470b546c8957dd94de8d2f5525ec", "sport": "NPB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="36" customHeight="1">
+      <c r="A143" s="24" t="inlineStr">
+        <is>
+          <t>27826062221f4e42</t>
+        </is>
+      </c>
+      <c r="B143" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:28:52.203222Z</t>
+        </is>
+      </c>
+      <c r="C143" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D143" s="24" t="inlineStr">
+        <is>
+          <t>156784</t>
+        </is>
+      </c>
+      <c r="E143" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F143" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="G143" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="H143" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I143" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J143" s="25" t="n"/>
+      <c r="K143" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L143" s="26" t="n">
+        <v>-270</v>
+      </c>
+      <c r="M143" s="27" t="n">
+        <v>1.37037</v>
+      </c>
+      <c r="N143" s="28" t="n">
+        <v>0.72973</v>
+      </c>
+      <c r="O143" s="28" t="n">
+        <v>0.62865</v>
+      </c>
+      <c r="P143" s="28" t="n"/>
+      <c r="Q143" s="28" t="n">
+        <v>-0.10108</v>
+      </c>
+      <c r="R143" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T143" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U143" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V143" s="24" t="n"/>
+      <c r="W143" s="26" t="n"/>
+      <c r="X143" s="26" t="n"/>
+      <c r="Y143" s="25" t="n"/>
+      <c r="Z143" s="26" t="n"/>
+      <c r="AA143" s="28" t="n"/>
+      <c r="AB143" s="28" t="n"/>
+      <c r="AC143" s="30" t="n"/>
+      <c r="AD143" s="24" t="n"/>
+      <c r="AE143" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.7300 (market_slug=aec-npb-fsh-nhf-2026-10-14). Tie probability=0.0239.</t>
+        </is>
+      </c>
+      <c r="AF143" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG143" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH143" s="24" t="n"/>
+      <c r="AI143" s="31" t="n"/>
+      <c r="AJ143" s="31" t="n"/>
+      <c r="AK143" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL143" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM143" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN143" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO143" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP143" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AQ143" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AR143" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AS143" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AT143" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AU143" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AV143" s="24" t="n"/>
+      <c r="AW143" s="24" t="n"/>
+      <c r="AX143" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY143" s="24" t="n"/>
+      <c r="AZ143" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA143" s="24" t="inlineStr">
+        <is>
+          <t>22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7</t>
+        </is>
+      </c>
+      <c r="BB143" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC143" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD143" s="24" t="inlineStr">
+        <is>
+          <t>22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7</t>
+        </is>
+      </c>
+      <c r="BE143" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF143" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG143" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH143" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:28:52.203222Z</t>
+        </is>
+      </c>
+      <c r="BI143" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ143" s="25" t="n"/>
+      <c r="BK143" s="26" t="n">
+        <v>-270</v>
+      </c>
+      <c r="BL143" s="27" t="n">
+        <v>1.37037</v>
+      </c>
+      <c r="BM143" s="28" t="n">
+        <v>0.72973</v>
+      </c>
+      <c r="BN143" s="28" t="n"/>
+      <c r="BO143" s="28" t="n"/>
+      <c r="BP143" s="25" t="n"/>
+      <c r="BQ143" s="27" t="n"/>
+      <c r="BR143" s="28" t="n"/>
+      <c r="BS143" s="28" t="n"/>
+      <c r="BT143" s="28" t="n"/>
+      <c r="BU143" s="25" t="n"/>
+      <c r="BV143" s="29" t="n"/>
+      <c r="BW143" s="24" t="n"/>
+      <c r="BX143" s="30" t="n"/>
+      <c r="BY143" s="27" t="n"/>
+      <c r="BZ143" s="24" t="n"/>
+      <c r="CA143" s="31" t="n"/>
+      <c r="CB143" s="24" t="n"/>
+      <c r="CC143" s="24" t="n"/>
+      <c r="CD143" s="24" t="n"/>
+      <c r="CE143" s="24" t="n"/>
+      <c r="CF143" s="24" t="n"/>
+      <c r="CG143" s="24" t="n"/>
+      <c r="CH143" s="24" t="n"/>
+      <c r="CI143" s="24" t="n"/>
+      <c r="CJ143" s="24" t="n"/>
+      <c r="CK143" s="24" t="n"/>
+      <c r="CL143" s="24" t="n"/>
+      <c r="CM143" s="24" t="n"/>
+      <c r="CN143" s="24" t="n"/>
+      <c r="CO143" s="24" t="n"/>
+      <c r="CP143" s="24" t="n"/>
+      <c r="CQ143" s="24" t="n"/>
+      <c r="CR143" s="24" t="n"/>
+      <c r="CS143" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT143" s="24" t="n"/>
+      <c r="CU143" s="24" t="n"/>
+      <c r="CV143" s="24" t="n"/>
+      <c r="CW143" s="24" t="n"/>
+      <c r="CX143" s="24" t="n"/>
+      <c r="CY143" s="24" t="n"/>
+      <c r="CZ143" s="24" t="n"/>
+      <c r="DA143" s="24" t="n"/>
+      <c r="DB143" s="24" t="n"/>
+      <c r="DC143" s="24" t="n"/>
+      <c r="DD143" s="24" t="n"/>
+      <c r="DE143" s="24" t="n"/>
+      <c r="DF143" s="24" t="n"/>
+      <c r="DG143" s="24" t="n"/>
+      <c r="DH143" s="24" t="n"/>
+      <c r="DI143" s="24" t="n"/>
+      <c r="DJ143" s="24" t="n"/>
+      <c r="DK143" s="24" t="n"/>
+      <c r="DL143" s="24" t="n"/>
+      <c r="DM143" s="24" t="n"/>
+      <c r="DN143" s="24" t="n"/>
+      <c r="DO143" s="24" t="n"/>
+      <c r="DP143" s="24" t="n"/>
+      <c r="DQ143" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7", "away_team": "Nippon Ham Fighters", "draw_settlement_value": 0.5, "event_id": "156784", "event_start_utc": "2026-10-14T09:00:00Z", "features": {"away_elo": 1560.298182, "base_tie_rate": 0.02386015, "home_advantage": 35.0, "home_elo": 1619.092388}, "historical_source_observation_times_verified": false, "home_team": "Fukuoka SoftBank Hawks", "inference_inputs": {"away_id": "F", "base_tie_rate": 0.02386015, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"F": 1560.298182, "H": 1619.092388}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "H", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-13T22:28:51.412639+00:00", "outcome_probabilities": {"away": 0.3594200900286334, "draw": 0.02386015, "home": 0.6167197599713666}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.37135, "home": 0.62865}, "snapshot_hash": "dc01d7b908dd35df8593618b3851718dbff44ad9bd138f6956a263f5cf17eb97", "sport": "NPB"}</t>
         </is>
       </c>
     </row>

--- a/data/sports/npb/gated.xlsx
+++ b/data/sports/npb/gated.xlsx
@@ -46180,12 +46180,12 @@
     <row r="142" ht="36" customHeight="1">
       <c r="A142" s="24" t="inlineStr">
         <is>
-          <t>bf57d1ea8d5a41ac</t>
+          <t>65b0259b9ca64be9</t>
         </is>
       </c>
       <c r="B142" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:28:52.203222Z</t>
+          <t>2026-10-14T05:52:01.251682Z</t>
         </is>
       </c>
       <c r="C142" s="24" t="inlineStr">
@@ -46230,20 +46230,20 @@
         </is>
       </c>
       <c r="L142" s="26" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="M142" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.641026</v>
       </c>
       <c r="N142" s="28" t="n">
-        <v>0.6</v>
+        <v>0.609375</v>
       </c>
       <c r="O142" s="28" t="n">
         <v>0.547141</v>
       </c>
       <c r="P142" s="28" t="n"/>
       <c r="Q142" s="28" t="n">
-        <v>-0.052859</v>
+        <v>-0.062234</v>
       </c>
       <c r="R142" s="26" t="n">
         <v>0</v>
@@ -46272,7 +46272,7 @@
       <c r="AD142" s="24" t="n"/>
       <c r="AE142" s="31" t="inlineStr">
         <is>
-          <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-npb-hta-ybo-2026-10-14). Tie probability=0.0239.</t>
+          <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-hta-ybo-2026-10-14). Tie probability=0.0239.</t>
         </is>
       </c>
       <c r="AF142" s="31" t="inlineStr">
@@ -46356,7 +46356,7 @@
       </c>
       <c r="BA142" s="24" t="inlineStr">
         <is>
-          <t>22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7</t>
+          <t>7fafc82f9fdb1d095962ad6674aded3d12f0af8cc89088ba34fd259b2b58c3d6</t>
         </is>
       </c>
       <c r="BB142" s="24" t="inlineStr">
@@ -46371,7 +46371,7 @@
       </c>
       <c r="BD142" s="24" t="inlineStr">
         <is>
-          <t>22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7</t>
+          <t>7fafc82f9fdb1d095962ad6674aded3d12f0af8cc89088ba34fd259b2b58c3d6</t>
         </is>
       </c>
       <c r="BE142" s="24" t="inlineStr">
@@ -46391,7 +46391,7 @@
       </c>
       <c r="BH142" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:28:51.878028Z</t>
+          <t>2026-10-14T05:52:00.939109Z</t>
         </is>
       </c>
       <c r="BI142" s="24" t="inlineStr">
@@ -46401,13 +46401,13 @@
       </c>
       <c r="BJ142" s="25" t="n"/>
       <c r="BK142" s="26" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="BL142" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.641026</v>
       </c>
       <c r="BM142" s="28" t="n">
-        <v>0.6</v>
+        <v>0.609375</v>
       </c>
       <c r="BN142" s="28" t="n"/>
       <c r="BO142" s="28" t="n"/>
@@ -46470,19 +46470,19 @@
       <c r="DP142" s="24" t="n"/>
       <c r="DQ142" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7", "away_team": "Yokohama BayStars", "draw_settlement_value": 0.5, "event_id": "154783", "event_start_utc": "2026-10-14T09:00:00Z", "features": {"away_elo": 1521.060932, "base_tie_rate": 0.02386015, "home_advantage": 35.0, "home_elo": 1519.723482}, "historical_source_observation_times_verified": false, "home_team": "Hanshin Tigers", "inference_inputs": {"away_id": "DB", "base_tie_rate": 0.02386015, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"DB": 1521.060932, "T": 1519.723482}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "T", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-13T22:28:51.412639+00:00", "outcome_probabilities": {"away": 0.4409289279790772, "draw": 0.02386015, "home": 0.5352109220209229}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.452859, "home": 0.547141}, "snapshot_hash": "7015e4880439a4d4afc64cf919c0221dc4d3470b546c8957dd94de8d2f5525ec", "sport": "NPB"}</t>
+          <t>{"artifact_hash": "7fafc82f9fdb1d095962ad6674aded3d12f0af8cc89088ba34fd259b2b58c3d6", "away_team": "Yokohama BayStars", "draw_settlement_value": 0.5, "event_id": "154783", "event_start_utc": "2026-10-14T09:00:00Z", "features": {"away_elo": 1521.060932, "base_tie_rate": 0.02386015, "home_advantage": 35.0, "home_elo": 1519.723482}, "historical_source_observation_times_verified": false, "home_team": "Hanshin Tigers", "inference_inputs": {"away_id": "DB", "base_tie_rate": 0.02386015, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"DB": 1521.060932, "T": 1519.723482}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "8d592e32eff91d945b870d7032edca3806863cff9428edece9f38d56cc36b070"}, "home_id": "T", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-14T05:52:00.228547+00:00", "outcome_probabilities": {"away": 0.4409289279790772, "draw": 0.02386015, "home": 0.5352109220209229}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.452859, "home": 0.547141}, "snapshot_hash": "b30406ee8db9b04dc143ff245b6267004e6131827375291eabdbdb240cef7142", "sport": "NPB"}</t>
         </is>
       </c>
     </row>
     <row r="143" ht="36" customHeight="1">
       <c r="A143" s="24" t="inlineStr">
         <is>
-          <t>27826062221f4e42</t>
+          <t>3fc2916b93bf49bc</t>
         </is>
       </c>
       <c r="B143" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:28:52.203222Z</t>
+          <t>2026-10-14T05:52:01.251682Z</t>
         </is>
       </c>
       <c r="C143" s="24" t="inlineStr">
@@ -46527,20 +46527,20 @@
         </is>
       </c>
       <c r="L143" s="26" t="n">
-        <v>-270</v>
+        <v>-317</v>
       </c>
       <c r="M143" s="27" t="n">
-        <v>1.37037</v>
+        <v>1.315457</v>
       </c>
       <c r="N143" s="28" t="n">
-        <v>0.72973</v>
+        <v>0.760192</v>
       </c>
       <c r="O143" s="28" t="n">
         <v>0.62865</v>
       </c>
       <c r="P143" s="28" t="n"/>
       <c r="Q143" s="28" t="n">
-        <v>-0.10108</v>
+        <v>-0.131542</v>
       </c>
       <c r="R143" s="26" t="n">
         <v>0</v>
@@ -46569,7 +46569,7 @@
       <c r="AD143" s="24" t="n"/>
       <c r="AE143" s="31" t="inlineStr">
         <is>
-          <t>Tie-aware Elo baseline; executable ask 0.7300 (market_slug=aec-npb-fsh-nhf-2026-10-14). Tie probability=0.0239.</t>
+          <t>Tie-aware Elo baseline; executable ask 0.7600 (market_slug=aec-npb-fsh-nhf-2026-10-14). Tie probability=0.0239.</t>
         </is>
       </c>
       <c r="AF143" s="31" t="inlineStr">
@@ -46653,7 +46653,7 @@
       </c>
       <c r="BA143" s="24" t="inlineStr">
         <is>
-          <t>22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7</t>
+          <t>7fafc82f9fdb1d095962ad6674aded3d12f0af8cc89088ba34fd259b2b58c3d6</t>
         </is>
       </c>
       <c r="BB143" s="24" t="inlineStr">
@@ -46668,7 +46668,7 @@
       </c>
       <c r="BD143" s="24" t="inlineStr">
         <is>
-          <t>22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7</t>
+          <t>7fafc82f9fdb1d095962ad6674aded3d12f0af8cc89088ba34fd259b2b58c3d6</t>
         </is>
       </c>
       <c r="BE143" s="24" t="inlineStr">
@@ -46688,7 +46688,7 @@
       </c>
       <c r="BH143" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:28:52.203222Z</t>
+          <t>2026-10-14T05:52:01.251682Z</t>
         </is>
       </c>
       <c r="BI143" s="24" t="inlineStr">
@@ -46698,13 +46698,13 @@
       </c>
       <c r="BJ143" s="25" t="n"/>
       <c r="BK143" s="26" t="n">
-        <v>-270</v>
+        <v>-317</v>
       </c>
       <c r="BL143" s="27" t="n">
-        <v>1.37037</v>
+        <v>1.315457</v>
       </c>
       <c r="BM143" s="28" t="n">
-        <v>0.72973</v>
+        <v>0.760192</v>
       </c>
       <c r="BN143" s="28" t="n"/>
       <c r="BO143" s="28" t="n"/>
@@ -46767,7 +46767,7 @@
       <c r="DP143" s="24" t="n"/>
       <c r="DQ143" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "22e0c0f1461fdef391a741fea246e299d8e3525613f2495e4a42a8edb46be7a7", "away_team": "Nippon Ham Fighters", "draw_settlement_value": 0.5, "event_id": "156784", "event_start_utc": "2026-10-14T09:00:00Z", "features": {"away_elo": 1560.298182, "base_tie_rate": 0.02386015, "home_advantage": 35.0, "home_elo": 1619.092388}, "historical_source_observation_times_verified": false, "home_team": "Fukuoka SoftBank Hawks", "inference_inputs": {"away_id": "F", "base_tie_rate": 0.02386015, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"F": 1560.298182, "H": 1619.092388}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "H", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-13T22:28:51.412639+00:00", "outcome_probabilities": {"away": 0.3594200900286334, "draw": 0.02386015, "home": 0.6167197599713666}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.37135, "home": 0.62865}, "snapshot_hash": "dc01d7b908dd35df8593618b3851718dbff44ad9bd138f6956a263f5cf17eb97", "sport": "NPB"}</t>
+          <t>{"artifact_hash": "7fafc82f9fdb1d095962ad6674aded3d12f0af8cc89088ba34fd259b2b58c3d6", "away_team": "Nippon Ham Fighters", "draw_settlement_value": 0.5, "event_id": "156784", "event_start_utc": "2026-10-14T09:00:00Z", "features": {"away_elo": 1560.298182, "base_tie_rate": 0.02386015, "home_advantage": 35.0, "home_elo": 1619.092388}, "historical_source_observation_times_verified": false, "home_team": "Fukuoka SoftBank Hawks", "inference_inputs": {"away_id": "F", "base_tie_rate": 0.02386015, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"F": 1560.298182, "H": 1619.092388}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "8d592e32eff91d945b870d7032edca3806863cff9428edece9f38d56cc36b070"}, "home_id": "H", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-14T05:52:00.228547+00:00", "outcome_probabilities": {"away": 0.3594200900286334, "draw": 0.02386015, "home": 0.6167197599713666}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.37135, "home": 0.62865}, "snapshot_hash": "7fb05bafaa59e8a12436558c3a0f6e4e36da1e7e98aed046bbfd1840373a0929", "sport": "NPB"}</t>
         </is>
       </c>
     </row>

--- a/data/sports/npb/gated.xlsx
+++ b/data/sports/npb/gated.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ143" headerRowCount="1">
-  <autoFilter ref="A1:DQ143"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ145" headerRowCount="1">
+  <autoFilter ref="A1:DQ145"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$143)</f>
+        <f>COUNTA('Picks'!$A$2:$A$145)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$143,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$145,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$143,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$145,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"win")+COUNTIFS('Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$145,"settled",'Picks'!$V$2:$V$145,"win")+COUNTIFS('Picks'!$U$2:$U$145,"settled",'Picks'!$V$2:$V$145,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$143,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$145,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$145,"&gt;0",'Picks'!$V$2:$V$145,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$145,"&gt;0",'Picks'!$V$2:$V$145,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"win")/(COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"win")+COUNTIFS('Picks'!$BX$2:$BX$143,"&gt;0",'Picks'!$V$2:$V$143,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$145,"&gt;0",'Picks'!$V$2:$V$145,"win")/(COUNTIFS('Picks'!$BX$2:$BX$145,"&gt;0",'Picks'!$V$2:$V$145,"win")+COUNTIFS('Picks'!$BX$2:$BX$145,"&gt;0",'Picks'!$V$2:$V$145,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$143)/SUM('Picks'!$BX$2:$BX$143),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$145)/SUM('Picks'!$BX$2:$BX$145),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$143)</f>
+        <f>SUM('Picks'!$BY$2:$BY$145)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$143,"&lt;&gt;",'Picks'!$AB$2:$AB$143),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$145,"&lt;&gt;",'Picks'!$AB$2:$AB$145),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$143,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$143,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$145,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$145,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$143,'Picks'!$AM$2:$AM$143,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$145,'Picks'!$AM$2:$AM$145,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$143,$A14,'Picks'!$U$2:$U$143,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$145,$A14,'Picks'!$U$2:$U$145,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$143,$A14,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$145,$A14,'Picks'!$U$2:$U$145,"settled",'Picks'!$V$2:$V$145,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$143,$A14,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$145,$A14,'Picks'!$U$2:$U$145,"settled",'Picks'!$V$2:$V$145,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$143,'Picks'!$H$2:$H$143,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$145,'Picks'!$H$2:$H$145,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$143,'Picks'!$H$2:$H$143,$A14,'Picks'!$U$2:$U$143,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$145,'Picks'!$H$2:$H$145,$A14,'Picks'!$U$2:$U$145,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$143,$A15,'Picks'!$U$2:$U$143,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$145,$A15,'Picks'!$U$2:$U$145,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$143,$A15,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$145,$A15,'Picks'!$U$2:$U$145,"settled",'Picks'!$V$2:$V$145,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$143,$A15,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$145,$A15,'Picks'!$U$2:$U$145,"settled",'Picks'!$V$2:$V$145,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$143,'Picks'!$H$2:$H$143,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$145,'Picks'!$H$2:$H$145,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$143,'Picks'!$H$2:$H$143,$A15,'Picks'!$U$2:$U$143,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$145,'Picks'!$H$2:$H$145,$A15,'Picks'!$U$2:$U$145,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$143,$A16,'Picks'!$U$2:$U$143,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$145,$A16,'Picks'!$U$2:$U$145,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$143,$A16,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$145,$A16,'Picks'!$U$2:$U$145,"settled",'Picks'!$V$2:$V$145,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$143,$A16,'Picks'!$U$2:$U$143,"settled",'Picks'!$V$2:$V$143,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$145,$A16,'Picks'!$U$2:$U$145,"settled",'Picks'!$V$2:$V$145,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$143,'Picks'!$H$2:$H$143,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$145,'Picks'!$H$2:$H$145,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$143,'Picks'!$H$2:$H$143,$A16,'Picks'!$U$2:$U$143,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$145,'Picks'!$H$2:$H$145,$A16,'Picks'!$U$2:$U$145,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ143"/>
+  <dimension ref="A1:DQ145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -46258,18 +46258,38 @@
       </c>
       <c r="U142" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V142" s="24" t="n"/>
-      <c r="W142" s="26" t="n"/>
-      <c r="X142" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V142" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W142" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X142" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y142" s="25" t="n"/>
-      <c r="Z142" s="26" t="n"/>
-      <c r="AA142" s="28" t="n"/>
-      <c r="AB142" s="28" t="n"/>
-      <c r="AC142" s="30" t="n"/>
-      <c r="AD142" s="24" t="n"/>
+      <c r="Z142" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="AA142" s="28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB142" s="28" t="n">
+        <v>0.000625</v>
+      </c>
+      <c r="AC142" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD142" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:04:58.045452Z</t>
+        </is>
+      </c>
       <c r="AE142" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-hta-ybo-2026-10-14). Tie probability=0.0239.</t>
@@ -46282,7 +46302,7 @@
       </c>
       <c r="AG142" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH142" s="24" t="n"/>
@@ -46412,8 +46432,12 @@
       <c r="BN142" s="28" t="n"/>
       <c r="BO142" s="28" t="n"/>
       <c r="BP142" s="25" t="n"/>
-      <c r="BQ142" s="27" t="n"/>
-      <c r="BR142" s="28" t="n"/>
+      <c r="BQ142" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BR142" s="28" t="n">
+        <v>0.61</v>
+      </c>
       <c r="BS142" s="28" t="n"/>
       <c r="BT142" s="28" t="n"/>
       <c r="BU142" s="25" t="n"/>
@@ -46555,18 +46579,38 @@
       </c>
       <c r="U143" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V143" s="24" t="n"/>
-      <c r="W143" s="26" t="n"/>
-      <c r="X143" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V143" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W143" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X143" s="26" t="n">
+        <v>6</v>
+      </c>
       <c r="Y143" s="25" t="n"/>
-      <c r="Z143" s="26" t="n"/>
-      <c r="AA143" s="28" t="n"/>
-      <c r="AB143" s="28" t="n"/>
-      <c r="AC143" s="30" t="n"/>
-      <c r="AD143" s="24" t="n"/>
+      <c r="Z143" s="26" t="n">
+        <v>-317</v>
+      </c>
+      <c r="AA143" s="28" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AB143" s="28" t="n">
+        <v>-0.000192</v>
+      </c>
+      <c r="AC143" s="30" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="AD143" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:04:58.972034Z</t>
+        </is>
+      </c>
       <c r="AE143" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.7600 (market_slug=aec-npb-fsh-nhf-2026-10-14). Tie probability=0.0239.</t>
@@ -46709,8 +46753,12 @@
       <c r="BN143" s="28" t="n"/>
       <c r="BO143" s="28" t="n"/>
       <c r="BP143" s="25" t="n"/>
-      <c r="BQ143" s="27" t="n"/>
-      <c r="BR143" s="28" t="n"/>
+      <c r="BQ143" s="27" t="n">
+        <v>1.315457</v>
+      </c>
+      <c r="BR143" s="28" t="n">
+        <v>0.76</v>
+      </c>
       <c r="BS143" s="28" t="n"/>
       <c r="BT143" s="28" t="n"/>
       <c r="BU143" s="25" t="n"/>
@@ -46771,6 +46819,600 @@
         </is>
       </c>
     </row>
+    <row r="144" ht="36" customHeight="1">
+      <c r="A144" s="24" t="inlineStr">
+        <is>
+          <t>54cfd20463514ad9</t>
+        </is>
+      </c>
+      <c r="B144" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:46:05.499523Z</t>
+        </is>
+      </c>
+      <c r="C144" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D144" s="24" t="inlineStr">
+        <is>
+          <t>156226</t>
+        </is>
+      </c>
+      <c r="E144" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F144" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="G144" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="H144" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I144" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J144" s="25" t="n"/>
+      <c r="K144" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L144" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M144" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N144" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O144" s="28" t="n">
+        <v>0.534905</v>
+      </c>
+      <c r="P144" s="28" t="n"/>
+      <c r="Q144" s="28" t="n">
+        <v>-0.124959</v>
+      </c>
+      <c r="R144" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T144" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U144" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V144" s="24" t="n"/>
+      <c r="W144" s="26" t="n"/>
+      <c r="X144" s="26" t="n"/>
+      <c r="Y144" s="25" t="n"/>
+      <c r="Z144" s="26" t="n"/>
+      <c r="AA144" s="28" t="n"/>
+      <c r="AB144" s="28" t="n"/>
+      <c r="AC144" s="30" t="n"/>
+      <c r="AD144" s="24" t="n"/>
+      <c r="AE144" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6600 (market_slug=aec-npb-hta-ybo-2026-10-15). Tie probability=0.0238.</t>
+        </is>
+      </c>
+      <c r="AF144" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG144" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH144" s="24" t="n"/>
+      <c r="AI144" s="31" t="n"/>
+      <c r="AJ144" s="31" t="n"/>
+      <c r="AK144" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL144" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM144" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN144" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO144" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP144" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AQ144" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AR144" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AS144" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AT144" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AU144" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AV144" s="24" t="n"/>
+      <c r="AW144" s="24" t="n"/>
+      <c r="AX144" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY144" s="24" t="n"/>
+      <c r="AZ144" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA144" s="24" t="inlineStr">
+        <is>
+          <t>825df62f7ca8ea80080b80e8de2f09e2cd7396038ed7b0fc994bf7724010e642</t>
+        </is>
+      </c>
+      <c r="BB144" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC144" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD144" s="24" t="inlineStr">
+        <is>
+          <t>825df62f7ca8ea80080b80e8de2f09e2cd7396038ed7b0fc994bf7724010e642</t>
+        </is>
+      </c>
+      <c r="BE144" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF144" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG144" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH144" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:46:05.438749Z</t>
+        </is>
+      </c>
+      <c r="BI144" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ144" s="25" t="n"/>
+      <c r="BK144" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL144" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM144" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN144" s="28" t="n"/>
+      <c r="BO144" s="28" t="n"/>
+      <c r="BP144" s="25" t="n"/>
+      <c r="BQ144" s="27" t="n"/>
+      <c r="BR144" s="28" t="n"/>
+      <c r="BS144" s="28" t="n"/>
+      <c r="BT144" s="28" t="n"/>
+      <c r="BU144" s="25" t="n"/>
+      <c r="BV144" s="29" t="n"/>
+      <c r="BW144" s="24" t="n"/>
+      <c r="BX144" s="30" t="n"/>
+      <c r="BY144" s="27" t="n"/>
+      <c r="BZ144" s="24" t="n"/>
+      <c r="CA144" s="31" t="n"/>
+      <c r="CB144" s="24" t="n"/>
+      <c r="CC144" s="24" t="n"/>
+      <c r="CD144" s="24" t="n"/>
+      <c r="CE144" s="24" t="n"/>
+      <c r="CF144" s="24" t="n"/>
+      <c r="CG144" s="24" t="n"/>
+      <c r="CH144" s="24" t="n"/>
+      <c r="CI144" s="24" t="n"/>
+      <c r="CJ144" s="24" t="n"/>
+      <c r="CK144" s="24" t="n"/>
+      <c r="CL144" s="24" t="n"/>
+      <c r="CM144" s="24" t="n"/>
+      <c r="CN144" s="24" t="n"/>
+      <c r="CO144" s="24" t="n"/>
+      <c r="CP144" s="24" t="n"/>
+      <c r="CQ144" s="24" t="n"/>
+      <c r="CR144" s="24" t="n"/>
+      <c r="CS144" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT144" s="24" t="n"/>
+      <c r="CU144" s="24" t="n"/>
+      <c r="CV144" s="24" t="n"/>
+      <c r="CW144" s="24" t="n"/>
+      <c r="CX144" s="24" t="n"/>
+      <c r="CY144" s="24" t="n"/>
+      <c r="CZ144" s="24" t="n"/>
+      <c r="DA144" s="24" t="n"/>
+      <c r="DB144" s="24" t="n"/>
+      <c r="DC144" s="24" t="n"/>
+      <c r="DD144" s="24" t="n"/>
+      <c r="DE144" s="24" t="n"/>
+      <c r="DF144" s="24" t="n"/>
+      <c r="DG144" s="24" t="n"/>
+      <c r="DH144" s="24" t="n"/>
+      <c r="DI144" s="24" t="n"/>
+      <c r="DJ144" s="24" t="n"/>
+      <c r="DK144" s="24" t="n"/>
+      <c r="DL144" s="24" t="n"/>
+      <c r="DM144" s="24" t="n"/>
+      <c r="DN144" s="24" t="n"/>
+      <c r="DO144" s="24" t="n"/>
+      <c r="DP144" s="24" t="n"/>
+      <c r="DQ144" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "825df62f7ca8ea80080b80e8de2f09e2cd7396038ed7b0fc994bf7724010e642", "away_team": "Yokohama BayStars", "draw_settlement_value": 0.5, "event_id": "156226", "event_start_utc": "2026-10-15T09:00:00Z", "features": {"away_elo": 1525.447278, "base_tie_rate": 0.02384888, "home_advantage": 35.0, "home_elo": 1515.337136}, "historical_source_observation_times_verified": false, "home_team": "Hanshin Tigers", "inference_inputs": {"away_id": "DB", "base_tie_rate": 0.02384888, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"DB": 1525.447278, "T": 1515.337136}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "8d592e32eff91d945b870d7032edca3806863cff9428edece9f38d56cc36b070"}, "home_id": "T", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-14T22:46:05.368217+00:00", "outcome_probabilities": {"away": 0.4531701196880638, "draw": 0.02384888, "home": 0.5229810003119363}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.465095, "home": 0.534905}, "snapshot_hash": "acf6820d40f58e4ca0f96699fe2d4db9c3d95828363255af30a1d7db203fb88e", "sport": "NPB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="36" customHeight="1">
+      <c r="A145" s="24" t="inlineStr">
+        <is>
+          <t>15548b5bd9f24398</t>
+        </is>
+      </c>
+      <c r="B145" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:46:05.499523Z</t>
+        </is>
+      </c>
+      <c r="C145" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D145" s="24" t="inlineStr">
+        <is>
+          <t>156785</t>
+        </is>
+      </c>
+      <c r="E145" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F145" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="G145" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="H145" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I145" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J145" s="25" t="n"/>
+      <c r="K145" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L145" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M145" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N145" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O145" s="28" t="n">
+        <v>0.636317</v>
+      </c>
+      <c r="P145" s="28" t="n"/>
+      <c r="Q145" s="28" t="n">
+        <v>0.016545</v>
+      </c>
+      <c r="R145" s="26" t="n">
+        <v>28</v>
+      </c>
+      <c r="S145" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T145" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U145" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V145" s="24" t="n"/>
+      <c r="W145" s="26" t="n"/>
+      <c r="X145" s="26" t="n"/>
+      <c r="Y145" s="25" t="n"/>
+      <c r="Z145" s="26" t="n"/>
+      <c r="AA145" s="28" t="n"/>
+      <c r="AB145" s="28" t="n"/>
+      <c r="AC145" s="30" t="n"/>
+      <c r="AD145" s="24" t="n"/>
+      <c r="AE145" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6200 (market_slug=aec-npb-fsh-nhf-2026-10-15). Tie probability=0.0238.</t>
+        </is>
+      </c>
+      <c r="AF145" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG145" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH145" s="24" t="n"/>
+      <c r="AI145" s="31" t="n"/>
+      <c r="AJ145" s="31" t="n"/>
+      <c r="AK145" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL145" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM145" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN145" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO145" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP145" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AQ145" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AR145" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AS145" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AT145" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AU145" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AV145" s="24" t="n"/>
+      <c r="AW145" s="24" t="n"/>
+      <c r="AX145" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY145" s="24" t="n"/>
+      <c r="AZ145" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA145" s="24" t="inlineStr">
+        <is>
+          <t>825df62f7ca8ea80080b80e8de2f09e2cd7396038ed7b0fc994bf7724010e642</t>
+        </is>
+      </c>
+      <c r="BB145" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC145" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD145" s="24" t="inlineStr">
+        <is>
+          <t>825df62f7ca8ea80080b80e8de2f09e2cd7396038ed7b0fc994bf7724010e642</t>
+        </is>
+      </c>
+      <c r="BE145" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF145" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG145" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH145" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:46:05.499523Z</t>
+        </is>
+      </c>
+      <c r="BI145" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ145" s="25" t="n"/>
+      <c r="BK145" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL145" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM145" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN145" s="28" t="n"/>
+      <c r="BO145" s="28" t="n"/>
+      <c r="BP145" s="25" t="n"/>
+      <c r="BQ145" s="27" t="n"/>
+      <c r="BR145" s="28" t="n"/>
+      <c r="BS145" s="28" t="n"/>
+      <c r="BT145" s="28" t="n"/>
+      <c r="BU145" s="25" t="n"/>
+      <c r="BV145" s="29" t="n"/>
+      <c r="BW145" s="24" t="n"/>
+      <c r="BX145" s="30" t="n"/>
+      <c r="BY145" s="27" t="n"/>
+      <c r="BZ145" s="24" t="n"/>
+      <c r="CA145" s="31" t="n"/>
+      <c r="CB145" s="24" t="n"/>
+      <c r="CC145" s="24" t="n"/>
+      <c r="CD145" s="24" t="n"/>
+      <c r="CE145" s="24" t="n"/>
+      <c r="CF145" s="24" t="n"/>
+      <c r="CG145" s="24" t="n"/>
+      <c r="CH145" s="24" t="n"/>
+      <c r="CI145" s="24" t="n"/>
+      <c r="CJ145" s="24" t="n"/>
+      <c r="CK145" s="24" t="n"/>
+      <c r="CL145" s="24" t="n"/>
+      <c r="CM145" s="24" t="n"/>
+      <c r="CN145" s="24" t="n"/>
+      <c r="CO145" s="24" t="n"/>
+      <c r="CP145" s="24" t="n"/>
+      <c r="CQ145" s="24" t="n"/>
+      <c r="CR145" s="24" t="n"/>
+      <c r="CS145" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT145" s="24" t="n"/>
+      <c r="CU145" s="24" t="n"/>
+      <c r="CV145" s="24" t="n"/>
+      <c r="CW145" s="24" t="n"/>
+      <c r="CX145" s="24" t="n"/>
+      <c r="CY145" s="24" t="n"/>
+      <c r="CZ145" s="24" t="n"/>
+      <c r="DA145" s="24" t="n"/>
+      <c r="DB145" s="24" t="n"/>
+      <c r="DC145" s="24" t="n"/>
+      <c r="DD145" s="24" t="n"/>
+      <c r="DE145" s="24" t="n"/>
+      <c r="DF145" s="24" t="n"/>
+      <c r="DG145" s="24" t="n"/>
+      <c r="DH145" s="24" t="n"/>
+      <c r="DI145" s="24" t="n"/>
+      <c r="DJ145" s="24" t="n"/>
+      <c r="DK145" s="24" t="n"/>
+      <c r="DL145" s="24" t="n"/>
+      <c r="DM145" s="24" t="n"/>
+      <c r="DN145" s="24" t="n"/>
+      <c r="DO145" s="24" t="n"/>
+      <c r="DP145" s="24" t="n"/>
+      <c r="DQ145" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "825df62f7ca8ea80080b80e8de2f09e2cd7396038ed7b0fc994bf7724010e642", "away_team": "Nippon Ham Fighters", "draw_settlement_value": 0.5, "event_id": "156785", "event_start_utc": "2026-10-15T09:00:00Z", "features": {"away_elo": 1557.352538, "base_tie_rate": 0.02384888, "home_advantage": 35.0, "home_elo": 1622.038032}, "historical_source_observation_times_verified": false, "home_team": "Fukuoka SoftBank Hawks", "inference_inputs": {"away_id": "F", "base_tie_rate": 0.02384888, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.0, "home_advantage": 35.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"F": 1557.352538, "H": 1622.038032}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "8d592e32eff91d945b870d7032edca3806863cff9428edece9f38d56cc36b070"}, "home_id": "H", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "npb-tie-aware-elo-v2", "observed_at_utc": "2026-10-14T22:46:05.368217+00:00", "outcome_probabilities": {"away": 0.35175820242487227, "draw": 0.02384888, "home": 0.6243929175751278}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.363683, "home": 0.636317}, "snapshot_hash": "2466aa23573c156d1651fe119740c418f306c08e4cbdcd51b46301025ecbf80b", "sport": "NPB"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
